--- a/9月振り返り_コーデTB建築.xlsx
+++ b/9月振り返り_コーデTB建築.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="254">
   <si>
     <r>
       <rPr>
@@ -82,7 +82,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026/09/01 → 09/28 </t>
+      <t xml:space="preserve">2026/09/01 → 09/30 </t>
     </r>
     <r>
       <rPr>
@@ -120,7 +120,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">405</t>
+      <t xml:space="preserve">381</t>
     </r>
     <r>
       <rPr>
@@ -699,9 +699,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">動きなし</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="8.5"/>
@@ -709,6 +706,36 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">動きなし（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF767676"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千円）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">総玉の増加はほぼ</t>
     </r>
     <r>
@@ -751,7 +778,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+13,815 </t>
+      <t xml:space="preserve">+13,874 </t>
     </r>
     <r>
       <rPr>
@@ -782,7 +809,28 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">玉はほぼ横ばい。増えたのは</t>
+      <t xml:space="preserve">玉はむしろ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-357 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">減りました。増えたのは</t>
     </r>
     <r>
       <rPr>
@@ -977,7 +1025,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">84%</t>
+      <t xml:space="preserve">83%</t>
     </r>
     <r>
       <rPr>
@@ -1103,7 +1151,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">91%</t>
+      <t xml:space="preserve">90%</t>
     </r>
     <r>
       <rPr>
@@ -1178,7 +1226,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-5,152</t>
+      <t xml:space="preserve">-5,258</t>
     </r>
     <r>
       <rPr>
@@ -1220,7 +1268,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+11,696 </t>
+      <t xml:space="preserve">+11,811 </t>
     </r>
     <r>
       <rPr>
@@ -1241,7 +1289,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+6,544 </t>
+      <t xml:space="preserve">+6,553 </t>
     </r>
     <r>
       <rPr>
@@ -1356,7 +1404,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ほぼ横ばい</t>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF767676"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月は減少</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1435,7 +1501,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+6,904 </t>
+      <t xml:space="preserve">+6,629 </t>
     </r>
     <r>
       <rPr>
@@ -1456,7 +1522,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+3,855 </t>
+      <t xml:space="preserve">+3,869 </t>
     </r>
     <r>
       <rPr>
@@ -1498,7 +1564,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-5,152 </t>
+      <t xml:space="preserve">-5,258 </t>
     </r>
     <r>
       <rPr>
@@ -1529,7 +1595,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">がほぼ打ち消しました。</t>
+      <t xml:space="preserve">が上回りました。</t>
     </r>
   </si>
   <si>
@@ -1562,7 +1628,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">玉は横ばい。来月以降に確度を上げられる玉のストックは増えていません。</t>
+      <t xml:space="preserve">玉は減少。来月以降に確度を上げられる玉のストックは増えていません。</t>
     </r>
   </si>
   <si>
@@ -1714,6 +1780,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">動きなし</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="8.5"/>
@@ -1861,7 +1930,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">17</t>
     </r>
     <r>
       <rPr>
@@ -1918,31 +1987,31 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月は横ばい）</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">月は </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10.5"/>
         <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">建築の玉が</t>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-357</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10.5"/>
         <color rgb="FF2C5F2D"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1951,6 +2020,27 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">建築の玉が</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10.5"/>
+        <color rgb="FF2C5F2D"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10.5"/>
+        <color rgb="FF2C5F2D"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">件のみ。増やす手を打つ</t>
     </r>
   </si>
@@ -2092,7 +2182,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年度内の金額。単位：千円。</t>
+      <t xml:space="preserve">年度内の金額。期間：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09/30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。単位：千円。</t>
     </r>
   </si>
   <si>
@@ -2541,6 +2669,42 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HOTEL THE MITSUI_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">補修</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2729,6 +2893,33 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">スターバックスロースタリー中目黒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プライスカード立て</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">味の素本社</t>
     </r>
     <r>
@@ -2957,6 +3148,50 @@
   </si>
   <si>
     <t xml:space="preserve">藍建材サンプル</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">味の素本社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アジパンダショップ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プライスカード立て（追加）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -3206,7 +3441,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">玉へ移ったぶんです。単位：千円。</t>
+      <t xml:space="preserve">玉へ移ったぶんです。期間：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09/30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。単位：千円。</t>
     </r>
   </si>
   <si>
@@ -3563,42 +3836,6 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HOTEL THE MITSUI_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">補修</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3691,77 +3928,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">図面およびモックアップ作成フェーズ</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">味の素本社</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">アジパンダショップ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">プライスカード立て（追加）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スターバックスロースタリー中目黒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">プライスカード立て</t>
     </r>
   </si>
   <si>
@@ -4082,6 +4248,12 @@
     <t xml:space="preserve">2026/09/11</t>
   </si>
   <si>
+    <t xml:space="preserve">イベント什器製作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/09/23</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -4171,12 +4343,34 @@
     <t xml:space="preserve">2026/08/08</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">05.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">施工調整</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">2026/09/28</t>
   </si>
   <si>
     <t xml:space="preserve">2026/10/02</t>
   </si>
   <si>
+    <t xml:space="preserve">2026/09/29</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026/09/25</t>
   </si>
   <si>
@@ -4184,6 +4378,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026/09/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/10/05</t>
   </si>
   <si>
     <r>
@@ -4254,6 +4451,36 @@
     <t xml:space="preserve">2026/12</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ホウライ様</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周年記念品</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/09</t>
+  </si>
+  <si>
     <t xml:space="preserve">2027/03</t>
   </si>
   <si>
@@ -4267,43 +4494,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">05.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">施工調整</t>
-    </r>
+      <t xml:space="preserve">07.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成約</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/09</t>
   </si>
   <si>
     <t xml:space="preserve">2026/10</t>
   </si>
   <si>
-    <t xml:space="preserve">2026/09</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">07.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">成約</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -4377,6 +4585,235 @@
     <t xml:space="preserve">2027/12</t>
   </si>
   <si>
+    <t xml:space="preserve">既存樹余り材活用プロジェクト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">●</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鷺沼駅前開発　既存樹活用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ソメイヨシノ・ノベルティ小物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2035/03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ラーメン店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">間仕切壁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不燃木材提案</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2030/03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千葉県商業施設改装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不燃木材</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/07</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">青森空港</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">地域材内装・什器</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2028/03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千葉県事業所内食堂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伐採木</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ジェスモナイト天板製作</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三井不動産レジデンシャル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_ChopValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加工</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2028/01</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -4404,16 +4841,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">●</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ラーメン店</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">池田山</t>
     </r>
     <r>
       <rPr>
@@ -4430,7 +4864,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">間仕切壁</t>
+      <t xml:space="preserve">既存樹アートオブジェ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">多摩産材</t>
     </r>
     <r>
       <rPr>
@@ -4447,20 +4891,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不燃木材提案</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2030/03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">池田山</t>
+      <t xml:space="preserve">飲食店カラトリ―什器</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">花博</t>
     </r>
     <r>
       <rPr>
@@ -4477,38 +4918,25 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">既存樹アートオブジェ</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三井不動産レジデンシャル</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_ChopValue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加工</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2028/01</t>
+      <t xml:space="preserve">日比谷花壇ブース</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ベンチ兼テーブル</t>
+    </r>
   </si>
   <si>
     <r>
@@ -4550,13 +4978,84 @@
     <t xml:space="preserve">2028/08</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">花博</t>
+    <t xml:space="preserve">藍建材羽目板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">滋賀県大津市</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">世田谷飲食店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_VE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提案壁材</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">02.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提案</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">かつくら新宿高島屋</t>
     </r>
     <r>
       <rPr>
@@ -4573,332 +5072,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日比谷花壇ブース</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ベンチ兼テーブル</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">多摩産材</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">飲食店カラトリ―什器</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">藍建材羽目板</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存樹余り材活用プロジェクト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/06</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">世田谷飲食店</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_VE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">提案壁材</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">提案</t>
+      <t xml:space="preserve">おくどんさん</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">秋田県産ドアハンドル</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ホウライ様</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周年記念品</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/09</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">千葉県事業所内食堂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伐採木</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ジェスモナイト天板製作</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2028/03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鷺沼駅前開発　既存樹活用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ソメイヨシノ・ノベルティ小物</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2035/03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">青森空港</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">地域材内装・什器</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">かつくら新宿高島屋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">おくどんさん</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">滋賀県大津市</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PJ</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/07</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">千葉県商業施設改装</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不燃木材</t>
-    </r>
   </si>
   <si>
     <r>
@@ -5419,7 +5597,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026/09/01 10:26 </t>
+      <t xml:space="preserve">2026/09/01 11:48 </t>
     </r>
     <r>
       <rPr>
@@ -5436,7 +5614,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026/09/28 15:37</t>
+      <t xml:space="preserve">2026/09/30 21:23</t>
     </r>
     <r>
       <rPr>
@@ -5453,7 +5631,193 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/29</t>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の全期間をカバー</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">除外</t>
+  </si>
+  <si>
+    <t xml:space="preserve">＊原価管理用＊ を含む商談</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 定義</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ABCD</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">総玉</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">玉 ＋ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">玉 ＋ 長期玉。フェーズ≠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">00_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失注 かつ 完了予定日が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年度（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/04/01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/03/31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）内</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AB</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">玉</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -5470,6 +5834,499 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。成約済み（フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）も含む</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CD</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">玉</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確度「長期」。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月は動きなし（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千円）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確度</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CD→AB</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">になったもの。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">玉からは減り、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">玉には増える</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 数字の作り方</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末 時点</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/10/05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スナップショット（★コーデ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TB_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">総商談</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年度 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">235</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の変更は未取得のため</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">9/30</t>
     </r>
     <r>
@@ -5478,17 +6335,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">の動きは含まれていません</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">除外</t>
-  </si>
-  <si>
-    <t xml:space="preserve">＊原価管理用＊ を含む商談</t>
-  </si>
-  <si>
-    <t xml:space="preserve">■ 定義</t>
+      <t xml:space="preserve">と同じとみなしています</t>
+    </r>
   </si>
   <si>
     <r>
@@ -5500,7 +6348,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ABCD</t>
+      <t xml:space="preserve">9/1 </t>
     </r>
     <r>
       <rPr>
@@ -5510,86 +6358,94 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">総玉</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">玉 ＋ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">玉 ＋ 長期玉。フェーズ≠</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">00_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">失注 かつ 完了予定日が</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年度（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/04/01</t>
+      <t xml:space="preserve">時点</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末 時点 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の増減 で逆算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の増減</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の商談変更履歴（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09/01</t>
     </r>
     <r>
       <rPr>
@@ -5606,15 +6462,49 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2027/03/31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）内</t>
+      <t xml:space="preserve">09/30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">381</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">89</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">商談を時系列で再生</t>
     </r>
   </si>
   <si>
@@ -5627,7 +6517,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">AB</t>
+      <t xml:space="preserve">9/1</t>
     </r>
     <r>
       <rPr>
@@ -5637,8 +6527,288 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">玉</t>
-    </r>
+      <t xml:space="preserve">時点の各項目</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">現在値から変更チェーンを逆向きに辿って復元（元の値→新しい値のループに対応）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期末値の補正</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スナップショットにある商談は期末値をそちらに合わせた（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降に入力された金額を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の動きに混ぜないため／該当</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件：秋田県産ドアハンドル </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">219</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千円）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">■ グラフ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配色</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">色覚多様性に配慮した</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">色（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CVD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分離 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ΔE 12.9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で検証済み）。すべてのグラフにデータラベルを表示</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">参照先</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「グラフ用データ」シート。増減明細シートから自動計算されます</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 注意点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">建築の絶対値</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★コーデ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">レポートに含まれないため未取得。建築の通期レポートがあれば同じ形で出せます</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新規</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件のうち</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）が金額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。見込みに乗っていない</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">集中度</t>
   </si>
   <si>
     <r>
@@ -5656,181 +6826,45 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。成約済み（フェーズ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">07</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）も含む</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CD</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">玉</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">確度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">確度「長期」。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月は動きなし（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">千円）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">確度</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">UP</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が認証桧柾目材供給</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5838,427 +6872,20 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CD→AB</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">になったもの。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">玉からは減り、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">玉には増える</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">■ 数字の作り方</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末 時点</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/10/05 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スナップショット（★コーデ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TB_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">総商談</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年度 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">235</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の変更は未取得のため同じとみなしています</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時点</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末 時点 − </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月の増減 で逆算</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月の増減</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の商談変更履歴</t>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目＋</t>
     </r>
     <r>
       <rPr>
@@ -6275,416 +6902,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">本（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">09/01-09/08</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">09/08-09/14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">09/14-09/28</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">405</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件を時系列で再生</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時点の各項目</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">現在値から変更チェーンを逆向きに辿って復元（元の値→新しい値のループに対応）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">重複</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ファイル間で重なる期間の同一変更は除外済み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">■ グラフ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配色</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">色覚多様性に配慮した</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">色（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CVD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分離 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ΔE 12.9 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で検証済み）。すべてのグラフにデータラベルを表示</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">参照先</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「グラフ用データ」シート。増減明細シートから自動計算されます</t>
-  </si>
-  <si>
-    <t xml:space="preserve">■ 注意点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">建築の絶対値</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">★コーデ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">レポートに含まれないため未取得。建築の通期レポートがあれば同じ形で出せます</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/29</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">変更履歴が未取得。厳密には「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/28</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時点」です</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新規</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">38</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件のうち</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">47%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）が金額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。見込みに乗っていない</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">集中度</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">確度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">91%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">が認証桧柾目材供給</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
+      <t xml:space="preserve">回目）の</t>
     </r>
     <r>
       <rPr>
@@ -6701,40 +6919,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回目＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目）の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">件／成約の</t>
     </r>
     <r>
@@ -6744,7 +6928,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">44%</t>
+      <t xml:space="preserve">38%</t>
     </r>
     <r>
       <rPr>
@@ -7921,7 +8105,7 @@
                 <c:formatCode>#,##0;\-#,##0;0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>85477</c:v>
+                  <c:v>85087</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>99318</c:v>
@@ -8007,7 +8191,7 @@
                 <c:formatCode>#,##0;\-#,##0;0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>183826</c:v>
+                  <c:v>184157</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>183800</c:v>
@@ -8104,11 +8288,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="39821797"/>
-        <c:axId val="59069199"/>
+        <c:axId val="19528694"/>
+        <c:axId val="42525580"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39821797"/>
+        <c:axId val="19528694"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8140,7 +8324,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59069199"/>
+        <c:crossAx val="42525580"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8148,7 +8332,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59069199"/>
+        <c:axId val="42525580"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8180,7 +8364,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39821797"/>
+        <c:crossAx val="19528694"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8444,10 +8628,10 @@
                 <c:formatCode>#,##0;\-#,##0;0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>11696</c:v>
+                  <c:v>11811</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1929</c:v>
+                  <c:v>2204</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>266</c:v>
@@ -8679,10 +8863,10 @@
                 <c:formatCode>#,##0;\-#,##0;0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6904</c:v>
+                  <c:v>6629</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3855</c:v>
+                  <c:v>3869</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8953,10 +9137,10 @@
                   <c:v>5597</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5152</c:v>
+                  <c:v>5258</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9414,7 +9598,7 @@
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="n">
         <f aca="false">グラフ用データ!E5</f>
-        <v>269603</v>
+        <v>269544</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -9426,13 +9610,13 @@
       <c r="G8" s="7"/>
       <c r="H8" s="8" t="n">
         <f aca="false">グラフ用データ!E7</f>
-        <v>13815</v>
+        <v>13874</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="9" t="n">
         <f aca="false">グラフ用データ!E7/グラフ用データ!E5</f>
-        <v>0.0512420114019503</v>
+        <v>0.0514721158697652</v>
       </c>
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
@@ -9500,13 +9684,13 @@
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="n">
         <f aca="false">グラフ用データ!B7</f>
-        <v>13841</v>
+        <v>14231</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="17" t="n">
         <f aca="false">グラフ用データ!C7</f>
-        <v>-26</v>
+        <v>-357</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
@@ -9518,7 +9702,7 @@
       <c r="J13" s="17"/>
       <c r="K13" s="18" t="n">
         <f aca="false">グラフ用データ!B7/グラフ用データ!E7</f>
-        <v>1.00188201230547</v>
+        <v>1.02573158425833</v>
       </c>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
@@ -9618,7 +9802,7 @@
     <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="n">
         <f aca="false">グラフ用データ!B5</f>
-        <v>85477</v>
+        <v>85087</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -9630,13 +9814,13 @@
       <c r="G36" s="7"/>
       <c r="H36" s="8" t="n">
         <f aca="false">グラフ用データ!B7</f>
-        <v>13841</v>
+        <v>14231</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
       <c r="K36" s="9" t="n">
         <f aca="false">グラフ用データ!B7/グラフ用データ!B5</f>
-        <v>0.161926600138049</v>
+        <v>0.167252341720827</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
@@ -9706,27 +9890,27 @@
     </row>
     <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="23" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"確度UP（CD→AB）",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
-        <v>11696</v>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"確度UP（CD→AB）",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
+        <v>11811</v>
       </c>
       <c r="C41" s="23"/>
       <c r="D41" s="23" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"新規作成",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
-        <v>1929</v>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"新規作成",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
+        <v>2204</v>
       </c>
       <c r="E41" s="23"/>
       <c r="F41" s="23" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"失注から復活",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"失注から復活",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>220</v>
       </c>
       <c r="G41" s="23"/>
       <c r="H41" s="24" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"増額",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"増額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>46</v>
       </c>
       <c r="I41" s="24"/>
       <c r="J41" s="25" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"減額",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"減額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>-50</v>
       </c>
       <c r="K41" s="25"/>
@@ -9735,27 +9919,27 @@
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="11" t="str">
-        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$23,"確度UP（CD→AB）",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
-        <v>5件</v>
+        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$26,"確度UP（CD→AB）",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")&amp;"件"</f>
+        <v>6件</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="str">
-        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$23,"新規作成",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
-        <v>11件</v>
+        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$26,"新規作成",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")&amp;"件"</f>
+        <v>13件</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="11" t="str">
-        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$23,"失注から復活",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
+        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$26,"失注から復活",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")&amp;"件"</f>
         <v>1件</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="26" t="str">
-        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$23,"増額",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
+        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$26,"増額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")&amp;"件"</f>
         <v>1件</v>
       </c>
       <c r="I42" s="26"/>
       <c r="J42" s="27" t="str">
-        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$23,"減額",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
+        <f aca="false">COUNTIFS('AB玉 増減明細'!$F$4:$F$26,"減額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")&amp;"件"</f>
         <v>1件</v>
       </c>
       <c r="K42" s="27"/>
@@ -9851,7 +10035,7 @@
     <row r="65" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="7" t="n">
         <f aca="false">グラフ用データ!C5</f>
-        <v>183826</v>
+        <v>184157</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -9863,13 +10047,13 @@
       <c r="G65" s="7"/>
       <c r="H65" s="29" t="n">
         <f aca="false">グラフ用データ!C7</f>
-        <v>-26</v>
+        <v>-357</v>
       </c>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="30" t="n">
         <f aca="false">グラフ用データ!C7/グラフ用データ!C5</f>
-        <v>-0.000141438099071948</v>
+        <v>-0.00193856329110487</v>
       </c>
       <c r="L65" s="30"/>
       <c r="M65" s="30"/>
@@ -9886,11 +10070,11 @@
       </c>
       <c r="F66" s="10"/>
       <c r="G66" s="10"/>
-      <c r="H66" s="20" t="s">
+      <c r="H66" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I66" s="20"/>
-      <c r="J66" s="20"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
       <c r="K66" s="26" t="s">
         <v>11</v>
       </c>
@@ -9939,28 +10123,28 @@
     </row>
     <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="23" t="n">
-        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"新規作成",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")</f>
-        <v>6904</v>
+        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"新規作成",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <v>6629</v>
       </c>
       <c r="C70" s="23"/>
       <c r="D70" s="23" t="n">
-        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"増額",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")</f>
-        <v>3855</v>
+        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"増額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <v>3869</v>
       </c>
       <c r="E70" s="23"/>
       <c r="F70" s="24" t="n">
-        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"確度UP（CD→AB）",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")</f>
-        <v>-5152</v>
+        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"確度UP（CD→AB）",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <v>-5258</v>
       </c>
       <c r="G70" s="24"/>
       <c r="H70" s="25" t="n">
-        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"失注",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")</f>
+        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"失注",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
         <v>-5597</v>
       </c>
       <c r="I70" s="25"/>
       <c r="J70" s="25" t="n">
-        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"減額",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")</f>
-        <v>-36</v>
+        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"減額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <v>0</v>
       </c>
       <c r="K70" s="25"/>
       <c r="L70" s="25"/>
@@ -9968,28 +10152,28 @@
     </row>
     <row r="71" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="11" t="str">
-        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$25,"新規作成",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")&amp;"件"</f>
-        <v>7件</v>
+        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$23,"新規作成",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
+        <v>5件</v>
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11" t="str">
-        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$25,"増額",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")&amp;"件"</f>
+        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$23,"増額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
         <v>4件</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="26" t="str">
-        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$25,"確度UP（CD→AB）",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")&amp;"件"</f>
-        <v>4件</v>
+        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$23,"確度UP（CD→AB）",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
+        <v>5件</v>
       </c>
       <c r="G71" s="26"/>
       <c r="H71" s="27" t="str">
-        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$25,"失注",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")&amp;"件"</f>
+        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$23,"失注",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
         <v>6件</v>
       </c>
       <c r="I71" s="27"/>
       <c r="J71" s="27" t="str">
-        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$25,"減額",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")&amp;"件"</f>
-        <v>1件</v>
+        <f aca="false">COUNTIFS('CD玉 増減明細'!$F$4:$F$23,"減額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")&amp;"件"</f>
+        <v>0件</v>
       </c>
       <c r="K71" s="27"/>
       <c r="L71" s="27"/>
@@ -10083,14 +10267,14 @@
     </row>
     <row r="94" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="32" t="n">
-        <f aca="false">SUM(成約明細!$C$4:$C$16)</f>
-        <v>14382</v>
+        <f aca="false">SUM(成約明細!$C$4:$C$22)</f>
+        <v>16525</v>
       </c>
       <c r="C94" s="32"/>
       <c r="D94" s="32"/>
       <c r="E94" s="33" t="n">
         <f aca="false">SUM(新規作成明細!$C$4:$C$41)</f>
-        <v>9345</v>
+        <v>10865</v>
       </c>
       <c r="F94" s="33"/>
       <c r="G94" s="33"/>
@@ -10102,15 +10286,15 @@
       <c r="J94" s="34"/>
       <c r="K94" s="35" t="n">
         <f aca="false">COUNTIF(新規作成明細!$G$4:$G$41,"●")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L94" s="35"/>
       <c r="M94" s="35"/>
     </row>
     <row r="95" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="11" t="str">
-        <f aca="false">13&amp;"件"</f>
-        <v>13件</v>
+        <f aca="false">19&amp;"件"</f>
+        <v>19件</v>
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
@@ -10128,7 +10312,7 @@
       <c r="J95" s="27"/>
       <c r="K95" s="27" t="str">
         <f aca="false">"件。新規"&amp;38&amp;"件の"&amp;TEXT(COUNTIF(新規作成明細!$G$4:$G$41,"●")/38,"0.0%")</f>
-        <v>件。新規38件の47.4%</v>
+        <v>件。新規38件の44.7%</v>
       </c>
       <c r="L95" s="27"/>
       <c r="M95" s="27"/>
@@ -10189,19 +10373,19 @@
     </row>
     <row r="100" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="8" t="n">
-        <f aca="false">SUMIF('AB玉 増減明細'!$A$4:$A$23,"建築",'AB玉 増減明細'!$E$4:$E$23)</f>
+        <f aca="false">SUMIF('AB玉 増減明細'!$A$4:$A$26,"建築",'AB玉 増減明細'!$E$4:$E$26)</f>
         <v>462</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
       <c r="E100" s="29" t="n">
-        <f aca="false">SUMIF('CD玉 増減明細'!$A$4:$A$25,"建築",'CD玉 増減明細'!$E$4:$E$25)</f>
+        <f aca="false">SUMIF('CD玉 増減明細'!$A$4:$A$23,"建築",'CD玉 増減明細'!$E$4:$E$23)</f>
         <v>0</v>
       </c>
       <c r="F100" s="29"/>
       <c r="G100" s="29"/>
       <c r="H100" s="36" t="n">
-        <f aca="false">SUMIF(成約明細!$A$4:$A$16,"建築",成約明細!$C$4:$C$16)</f>
+        <f aca="false">SUMIF(成約明細!$A$4:$A$22,"建築",成約明細!$C$4:$C$22)</f>
         <v>535</v>
       </c>
       <c r="I100" s="36"/>
@@ -10219,24 +10403,24 @@
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
       <c r="E101" s="20" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F101" s="20"/>
       <c r="G101" s="20"/>
       <c r="H101" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I101" s="11"/>
       <c r="J101" s="11"/>
       <c r="K101" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L101" s="20"/>
       <c r="M101" s="20"/>
     </row>
     <row r="103" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
@@ -10252,7 +10436,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
@@ -10268,44 +10452,44 @@
     </row>
     <row r="105" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C105" s="38"/>
       <c r="D105" s="38"/>
       <c r="E105" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F105" s="38"/>
       <c r="G105" s="38"/>
       <c r="H105" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I105" s="38"/>
       <c r="J105" s="38"/>
       <c r="K105" s="38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L105" s="38"/>
       <c r="M105" s="38"/>
     </row>
     <row r="106" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C106" s="39"/>
       <c r="D106" s="39"/>
       <c r="E106" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F106" s="39"/>
       <c r="G106" s="39"/>
       <c r="H106" s="40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I106" s="40"/>
       <c r="J106" s="40"/>
       <c r="K106" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L106" s="39"/>
       <c r="M106" s="39"/>
@@ -10493,7 +10677,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19"/>
@@ -10506,46 +10690,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="46" t="n">
         <v>0</v>
@@ -10557,21 +10741,21 @@
         <v>7616</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4" s="48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="50" t="n">
         <v>0</v>
@@ -10583,21 +10767,21 @@
         <v>3000</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="46" t="n">
         <v>0</v>
@@ -10612,44 +10796,44 @@
         <v>26</v>
       </c>
       <c r="G6" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="50" t="n">
-        <v>500</v>
+        <v>545</v>
       </c>
       <c r="E7" s="51" t="n">
-        <v>500</v>
+        <v>545</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="46" t="n">
         <v>0</v>
@@ -10664,18 +10848,18 @@
         <v>26</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="50" t="n">
         <v>0</v>
@@ -10687,44 +10871,44 @@
         <v>430</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>83</v>
+        <v>71</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>84</v>
       </c>
       <c r="C10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="46" t="n">
-        <v>220</v>
+        <v>265</v>
       </c>
       <c r="E10" s="47" t="n">
-        <v>220</v>
+        <v>265</v>
       </c>
       <c r="F10" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="48" t="s">
-        <v>84</v>
+        <v>26</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>79</v>
       </c>
       <c r="H10" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="49" t="s">
         <v>85</v>
@@ -10733,331 +10917,409 @@
         <v>0</v>
       </c>
       <c r="D11" s="50" t="n">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="E11" s="51" t="n">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="F11" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>78</v>
+        <v>27</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>86</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="46" t="n">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="E12" s="47" t="n">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="48" t="s">
-        <v>73</v>
+        <v>26</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>79</v>
       </c>
       <c r="H12" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="50" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E13" s="51" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="49" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>74</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="46" t="n">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="E14" s="47" t="n">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="F14" s="45" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H14" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="50" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="E15" s="51" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="F15" s="49" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="46" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E16" s="47" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="F16" s="45" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="50" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E17" s="51" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>74</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C18" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="46" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E18" s="47" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F18" s="45" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H18" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" s="50" t="n">
-        <v>1570</v>
+        <v>0</v>
       </c>
       <c r="D19" s="50" t="n">
-        <v>1616</v>
+        <v>62</v>
       </c>
       <c r="E19" s="51" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F19" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="52" t="s">
-        <v>76</v>
+        <v>26</v>
+      </c>
+      <c r="G19" s="49" t="s">
+        <v>79</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="46" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E20" s="47" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F20" s="45" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>95</v>
+        <v>71</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>96</v>
       </c>
       <c r="C21" s="50" t="n">
-        <v>0</v>
+        <v>1570</v>
       </c>
       <c r="D21" s="50" t="n">
-        <v>37</v>
+        <v>1616</v>
       </c>
       <c r="E21" s="51" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F21" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="49" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="G21" s="52" t="s">
+        <v>77</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C22" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="46" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E22" s="47" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F22" s="45" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H22" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="50" t="n">
+        <v>37</v>
+      </c>
+      <c r="E23" s="51" t="n">
+        <v>37</v>
+      </c>
+      <c r="F23" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="46" t="n">
         <v>2000</v>
       </c>
-      <c r="D23" s="50" t="n">
+      <c r="D26" s="46" t="n">
         <v>1950</v>
       </c>
-      <c r="E23" s="51" t="n">
+      <c r="E26" s="47" t="n">
         <v>-50</v>
       </c>
-      <c r="F23" s="49" t="s">
+      <c r="F26" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="52" t="s">
-        <v>76</v>
+      <c r="G26" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="48" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -11076,7 +11338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19"/>
@@ -11089,46 +11351,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C4" s="46" t="n">
         <v>0</v>
@@ -11143,18 +11405,18 @@
         <v>26</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C5" s="50" t="n">
         <v>0</v>
@@ -11169,18 +11431,18 @@
         <v>28</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C6" s="46" t="n">
         <v>1000</v>
@@ -11195,44 +11457,44 @@
         <v>28</v>
       </c>
       <c r="G6" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C7" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="50" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="E7" s="51" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="F7" s="49" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C8" s="46" t="n">
         <v>0</v>
@@ -11247,18 +11509,18 @@
         <v>26</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C9" s="50" t="n">
         <v>920</v>
@@ -11273,241 +11535,241 @@
         <v>28</v>
       </c>
       <c r="G9" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="48" t="s">
-        <v>108</v>
+        <v>71</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>112</v>
       </c>
       <c r="C10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="46" t="n">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="E10" s="47" t="n">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="F10" s="45" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C11" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="50" t="n">
-        <v>235</v>
+        <v>120</v>
       </c>
       <c r="E11" s="51" t="n">
-        <v>235</v>
+        <v>120</v>
       </c>
       <c r="F11" s="49" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="46" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E12" s="47" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F12" s="45" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C13" s="50" t="n">
+        <v>106</v>
+      </c>
+      <c r="D13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="50" t="n">
-        <v>80</v>
-      </c>
       <c r="E13" s="51" t="n">
-        <v>80</v>
+        <v>-106</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="49" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>74</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>112</v>
+        <v>71</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>115</v>
       </c>
       <c r="C14" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="D14" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="46" t="n">
-        <v>10</v>
-      </c>
       <c r="E14" s="47" t="n">
-        <v>10</v>
+        <v>-140</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="45" t="s">
-        <v>78</v>
+        <v>36</v>
+      </c>
+      <c r="G14" s="48" t="s">
+        <v>74</v>
       </c>
       <c r="H14" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>113</v>
+        <v>71</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>83</v>
       </c>
       <c r="C15" s="50" t="n">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="D15" s="50" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E15" s="51" t="n">
-        <v>-36</v>
+        <v>-300</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G15" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>114</v>
+        <v>71</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>80</v>
       </c>
       <c r="C16" s="46" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="D16" s="46" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="47" t="n">
-        <v>-140</v>
+        <v>-500</v>
       </c>
       <c r="F16" s="45" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G16" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H16" s="48" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="52" t="s">
-        <v>82</v>
+        <v>71</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>116</v>
       </c>
       <c r="C17" s="50" t="n">
-        <v>300</v>
+        <v>785</v>
       </c>
       <c r="D17" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="51" t="n">
-        <v>-300</v>
+        <v>-785</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="G17" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C18" s="46" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D18" s="46" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="47" t="n">
-        <v>-500</v>
+        <v>-800</v>
       </c>
       <c r="F18" s="45" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="G18" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H18" s="48" t="s">
         <v>74</v>
@@ -11515,184 +11777,132 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C19" s="50" t="n">
-        <v>785</v>
+        <v>1000</v>
       </c>
       <c r="D19" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="51" t="n">
-        <v>-785</v>
+        <v>-1000</v>
       </c>
       <c r="F19" s="49" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G19" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C20" s="46" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="D20" s="46" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="47" t="n">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="F20" s="45" t="s">
         <v>36</v>
       </c>
       <c r="G20" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H20" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="C21" s="50" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="D21" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="51" t="n">
-        <v>-1000</v>
+        <v>-1300</v>
       </c>
       <c r="F21" s="49" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="G21" s="52" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C22" s="46" t="n">
-        <v>1000</v>
+        <v>1572</v>
       </c>
       <c r="D22" s="46" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="47" t="n">
-        <v>-1000</v>
+        <v>-1572</v>
       </c>
       <c r="F22" s="45" t="s">
         <v>36</v>
       </c>
       <c r="G22" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H22" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="C23" s="50" t="n">
-        <v>1300</v>
+        <v>3352</v>
       </c>
       <c r="D23" s="50" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="51" t="n">
-        <v>-1300</v>
+        <v>-3352</v>
       </c>
       <c r="F23" s="49" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G23" s="52" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H23" s="52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="46" t="n">
-        <v>1572</v>
-      </c>
-      <c r="D24" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="47" t="n">
-        <v>-1572</v>
-      </c>
-      <c r="F24" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="48" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="50" t="n">
-        <v>3352</v>
-      </c>
-      <c r="D25" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="51" t="n">
-        <v>-3352</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="52" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -11711,7 +11921,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19"/>
@@ -11723,179 +11933,179 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="53" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C4" s="46" t="n">
         <v>3640</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="50" t="n">
         <v>3000</v>
       </c>
       <c r="D5" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E5" s="52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C6" s="46" t="n">
         <v>3000</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C7" s="50" t="n">
         <v>1950</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8" s="46" t="n">
-        <v>1384</v>
+        <v>1475</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>134</v>
+        <v>71</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>135</v>
       </c>
       <c r="C9" s="50" t="n">
-        <v>535</v>
+        <v>1384</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>430</v>
+        <v>535</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>87</v>
+        <v>71</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>83</v>
       </c>
       <c r="C11" s="50" t="n">
-        <v>149</v>
+        <v>430</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>88</v>
+        <v>71</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>84</v>
       </c>
       <c r="C12" s="46" t="n">
-        <v>120</v>
+        <v>265</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E12" s="48" t="s">
         <v>138</v>
@@ -11903,70 +12113,172 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C13" s="50" t="n">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C14" s="46" t="n">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E14" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C15" s="50" t="n">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>120</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="50" t="n">
         <v>70</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="46" t="n">
+      <c r="D17" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>62</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="50" t="n">
+        <v>62</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>38</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="50" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>141</v>
+      <c r="D21" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -11998,869 +12310,867 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="53" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C4" s="46" t="n">
         <v>5834</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G4" s="45"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>155</v>
       </c>
       <c r="C5" s="50" t="n">
-        <v>1128</v>
+        <v>1520</v>
       </c>
       <c r="D5" s="52" t="s">
         <v>74</v>
       </c>
       <c r="E5" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F5" s="52" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G5" s="49"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>81</v>
+        <v>71</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>78</v>
       </c>
       <c r="C6" s="46" t="n">
-        <v>462</v>
+        <v>1128</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G6" s="45"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>106</v>
+        <v>81</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>82</v>
       </c>
       <c r="C7" s="50" t="n">
-        <v>360</v>
+        <v>462</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G7" s="49"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C8" s="46" t="n">
-        <v>265</v>
+        <v>360</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G8" s="45"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="49" t="s">
-        <v>109</v>
+        <v>71</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>84</v>
       </c>
       <c r="C9" s="50" t="n">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G9" s="49"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F10" s="48" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G10" s="45"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="49" t="s">
         <v>87</v>
       </c>
       <c r="C11" s="50" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G11" s="49"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" s="46" t="n">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F12" s="48" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C13" s="50" t="n">
         <v>120</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G13" s="49"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" s="46" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14" s="48" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F14" s="48" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C15" s="50" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="F15" s="52" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="G15" s="49"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C16" s="46" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E16" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="48" t="s">
         <v>154</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>153</v>
       </c>
       <c r="G16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C17" s="50" t="n">
         <v>62</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G17" s="49"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C18" s="46" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E18" s="48" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F18" s="48" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G18" s="45"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="52" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C19" s="50" t="n">
         <v>50</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F19" s="52" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G19" s="49"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" s="46" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D20" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E20" s="48" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F20" s="48" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>95</v>
+        <v>71</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>97</v>
       </c>
       <c r="C21" s="50" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G21" s="49"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="45" t="s">
-        <v>96</v>
+        <v>71</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>98</v>
       </c>
       <c r="C22" s="46" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="F22" s="48" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G22" s="45"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C23" s="50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G23" s="49"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="C24" s="46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="F24" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="48" t="s">
-        <v>158</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="G24" s="45"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C25" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E25" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G25" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C26" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="G26" s="48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C27" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E27" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G27" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="48" t="s">
-        <v>164</v>
+        <v>71</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>171</v>
       </c>
       <c r="C28" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="48" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G28" s="48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C29" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="G29" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C30" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="48" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E30" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F30" s="48" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="G30" s="48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C31" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="52" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G31" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C32" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="48" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="48" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="G32" s="48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C33" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="52" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C34" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="48" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E34" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G34" s="48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C35" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="52" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E35" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F35" s="52" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="G35" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="45" t="s">
-        <v>177</v>
+        <v>71</v>
+      </c>
+      <c r="B36" s="48" t="s">
+        <v>182</v>
       </c>
       <c r="C36" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E36" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F36" s="48" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G36" s="48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C37" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="52" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F37" s="52" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G37" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C38" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="48" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E38" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F38" s="48" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G38" s="48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C39" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E39" s="52" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="F39" s="52" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G39" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C40" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="48" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E40" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F40" s="48" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="G40" s="48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C41" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E41" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F41" s="52" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="G41" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -12891,182 +13201,182 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="41" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="53" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" s="46" t="n">
         <v>1572</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="50" t="n">
         <v>1300</v>
       </c>
       <c r="D5" s="52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C6" s="46" t="n">
         <v>1000</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="50" t="n">
         <v>800</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" s="46" t="n">
         <v>785</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="50" t="n">
         <v>140</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C11" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -13094,54 +13404,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="54" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="53" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="55" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="57" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B5" s="58" t="n">
-        <f aca="false">B6-SUMIF('AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON",'AB玉 増減明細'!$E$4:$E$23)</f>
-        <v>85477</v>
+        <f aca="false">B6-SUMIF('AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON",'AB玉 増減明細'!$E$4:$E$26)</f>
+        <v>85087</v>
       </c>
       <c r="C5" s="58" t="n">
-        <f aca="false">C6-SUMIF('CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON",'CD玉 増減明細'!$E$4:$E$25)</f>
-        <v>183826</v>
+        <f aca="false">C6-SUMIF('CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON",'CD玉 増減明細'!$E$4:$E$23)</f>
+        <v>184157</v>
       </c>
       <c r="D5" s="59" t="n">
         <v>300</v>
       </c>
       <c r="E5" s="60" t="n">
         <f aca="false">SUM(B5:D5)</f>
-        <v>269603</v>
+        <v>269544</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="57" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B6" s="59" t="n">
         <v>99318</v>
@@ -13163,11 +13473,11 @@
       </c>
       <c r="B7" s="62" t="n">
         <f aca="false">B6-B5</f>
-        <v>13841</v>
+        <v>14231</v>
       </c>
       <c r="C7" s="62" t="n">
         <f aca="false">C6-C5</f>
-        <v>-26</v>
+        <v>-357</v>
       </c>
       <c r="D7" s="62" t="n">
         <f aca="false">D6-D5</f>
@@ -13175,21 +13485,21 @@
       </c>
       <c r="E7" s="62" t="n">
         <f aca="false">E6-E5</f>
-        <v>13815</v>
+        <v>13874</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="63" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" s="58" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"確度UP（CD→AB）",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
-        <v>11696</v>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"確度UP（CD→AB）",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
+        <v>11811</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13197,31 +13507,31 @@
         <v>26</v>
       </c>
       <c r="B11" s="58" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"新規作成",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
-        <v>1929</v>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"新規作成",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
+        <v>2204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B12" s="58" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"失注から復活",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")+SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"増額",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"失注から復活",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")+SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"増額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="64" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B13" s="65" t="n">
-        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$23,'AB玉 増減明細'!$F$4:$F$23,"減額",'AB玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"減額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>-50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="63" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13229,8 +13539,8 @@
         <v>26</v>
       </c>
       <c r="B17" s="58" t="n">
-        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"新規作成",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")</f>
-        <v>6904</v>
+        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"新規作成",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <v>6629</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13238,13 +13548,13 @@
         <v>28</v>
       </c>
       <c r="B18" s="58" t="n">
-        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"増額",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON")</f>
-        <v>3855</v>
+        <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"増額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
+        <v>3869</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="66" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13252,17 +13562,17 @@
         <v>36</v>
       </c>
       <c r="B21" s="58" t="n">
-        <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"失注",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON"))</f>
+        <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"失注",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
         <v>5597</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="45" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B22" s="58" t="n">
-        <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"確度UP（CD→AB）",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON"))</f>
-        <v>5152</v>
+        <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"確度UP（CD→AB）",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
+        <v>5258</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13270,8 +13580,8 @@
         <v>29</v>
       </c>
       <c r="B23" s="58" t="n">
-        <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$25,'CD玉 増減明細'!$F$4:$F$25,"減額",'CD玉 増減明細'!$A$4:$A$25,"コーデ+TREEBATON"))</f>
-        <v>36</v>
+        <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"減額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13290,7 +13600,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -13299,37 +13609,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="54" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="67" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B3" s="68"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="69" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B4" s="70" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="69" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B5" s="68" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="69" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13338,48 +13648,48 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="67" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B8" s="70"/>
     </row>
     <row r="9" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="72" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B9" s="68" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="72" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B10" s="70" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="72" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B11" s="70" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="69" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B12" s="70" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="69" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B13" s="68" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13388,48 +13698,48 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B15" s="70"/>
     </row>
     <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="72" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B16" s="68" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="72" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B17" s="68" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="72" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B18" s="68" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="72" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B19" s="70" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="69" t="s">
-        <v>234</v>
-      </c>
-      <c r="B20" s="70" t="s">
-        <v>235</v>
+        <v>239</v>
+      </c>
+      <c r="B20" s="68" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13438,24 +13748,24 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="67" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B22" s="70"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="69" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="69" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B24" s="70" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13464,48 +13774,40 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B26" s="70"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="69" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B27" s="70" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="72" t="s">
-        <v>244</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="69" t="s">
+        <v>153</v>
       </c>
       <c r="B28" s="70" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="69" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="B29" s="70" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="69" t="s">
-        <v>247</v>
-      </c>
-      <c r="B30" s="70" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="72" t="s">
-        <v>249</v>
-      </c>
-      <c r="B31" s="68" t="s">
-        <v>250</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="72" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" s="68" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/9月振り返り_コーデTB建築.xlsx
+++ b/9月振り返り_コーデTB建築.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="286">
   <si>
     <r>
       <rPr>
@@ -1674,7 +1674,1961 @@
     <t xml:space="preserve">新規のうち金額未入力</t>
   </si>
   <si>
-    <t xml:space="preserve">⑤　建築</t>
+    <t xml:space="preserve">⑤　今月のトピック</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数字に表れた出来事と、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF767676"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の数字との対応です。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">トピック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何があったか</t>
+  </si>
+  <si>
+    <t xml:space="preserve">関連する数字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">次の展開</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リリカラさん</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コンペ対応が完了。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に商談レコードなし（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の変更履歴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">381</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スナップショット</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">235</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件のいずれにも該当なし）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果が出たら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に起票する。受注なら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月以降の玉に乗る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF2C5F2D"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CUE</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF2C5F2D"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">さん</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">イベント什器を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に成約。確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B→A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、完了予定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1,475</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月成約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件のうち</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番目）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">森林の仕事</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Park</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（なんば）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">森の体感ブース </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）が継続中</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF2C5F2D"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ATONA</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF2C5F2D"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（乃村工藝社）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">京都案件の納品・請求・売上計上が完了。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の成約ではなく、成約済み案件の売上計上です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">売上計上 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8,480</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（内装突板 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,580</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FFE 5,900</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。京都全体では </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11,751</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">由布院 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ATONA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">箱根 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・鹿児島</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">屋久島 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">内閣府 檜板</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に成約。商談名を「内閣総理大臣就任用木札」から変更。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+149</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D→A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、完了予定 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11/30→9/28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に前倒し</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">金額は小さいが実績として使える。同種案件の横展開先を探す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ホウライさん</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千本松牧場</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月に成約。林内ベンチは追加依頼も入った。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6,334</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（④小サイン・林内ベンチ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／⑤記念品 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,950</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／ホウライ様予算ベンチ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,384</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月成約の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周年記念品 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,520</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に新規起票。アクリル板後納品分 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">素朴屋さん</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年内の納品スケジュールが固まった。認証桧柾目材供給</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目まで見えた。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">累計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24,545</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8,095</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月成約／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月成約／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7,616</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,834</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝確度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+7,616</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">玉増加の最大要因。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化が次の山</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リリカラさんのコンペは</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SF</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFB04A3C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に商談が登録されていません。結果にかかわらず起票しておかないと、動いた事実が数字に残りません。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CUE</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・内閣府・ホウライ・素朴屋の</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件で</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月成約の</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">66%</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10,958</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16,525</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ATONA</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は売上計上 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8,480 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFC87941"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が別途あります。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⑥　建築</t>
   </si>
   <si>
     <t xml:space="preserve">建築案件は通期スナップショットのレポートが未取得のため、増減のみ表示しています。</t>
@@ -1872,7 +3826,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">⑥　来月に向けて</t>
+    <t xml:space="preserve">⑦　来月に向けて</t>
   </si>
   <si>
     <t xml:space="preserve">この振り返りから出てくる打ち手です。</t>
@@ -7107,7 +9061,7 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="60">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7332,6 +9286,61 @@
       <name val="Meiryo"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FFB04A3C"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFB04A3C"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFB04A3C"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FF2C5F2D"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FF2C5F2D"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -7618,7 +9627,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="82">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7763,11 +9772,47 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7775,15 +9820,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7791,43 +9836,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="42" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="50" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="50" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7835,51 +9880,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="55" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="55" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7887,27 +9932,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8288,11 +10333,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="19528694"/>
-        <c:axId val="42525580"/>
+        <c:axId val="70636339"/>
+        <c:axId val="72114459"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19528694"/>
+        <c:axId val="70636339"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8324,7 +10369,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42525580"/>
+        <c:crossAx val="72114459"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8332,7 +10377,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42525580"/>
+        <c:axId val="72114459"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8364,7 +10409,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19528694"/>
+        <c:crossAx val="70636339"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9501,7 +11546,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:M107"/>
+  <dimension ref="B2:M120"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.2"/>
@@ -10349,167 +12394,385 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
     </row>
-    <row r="99" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B99" s="13" t="s">
+    <row r="99" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B99" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C99" s="36"/>
+      <c r="D99" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E99" s="36"/>
+      <c r="F99" s="36"/>
+      <c r="G99" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="H99" s="36"/>
+      <c r="I99" s="36"/>
+      <c r="J99" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="K99" s="36"/>
+      <c r="L99" s="36"/>
+      <c r="M99" s="36"/>
+    </row>
+    <row r="100" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B100" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C100" s="37"/>
+      <c r="D100" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
+      <c r="J100" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="K100" s="38"/>
+      <c r="L100" s="38"/>
+      <c r="M100" s="38"/>
+    </row>
+    <row r="101" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B101" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C101" s="40"/>
+      <c r="D101" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="E101" s="41"/>
+      <c r="F101" s="41"/>
+      <c r="G101" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H101" s="41"/>
+      <c r="I101" s="41"/>
+      <c r="J101" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="K101" s="41"/>
+      <c r="L101" s="41"/>
+      <c r="M101" s="41"/>
+    </row>
+    <row r="102" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B102" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C102" s="40"/>
+      <c r="D102" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E102" s="41"/>
+      <c r="F102" s="41"/>
+      <c r="G102" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="H102" s="41"/>
+      <c r="I102" s="41"/>
+      <c r="J102" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K102" s="41"/>
+      <c r="L102" s="41"/>
+      <c r="M102" s="41"/>
+    </row>
+    <row r="103" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B103" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C103" s="42"/>
+      <c r="D103" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="E103" s="43"/>
+      <c r="F103" s="43"/>
+      <c r="G103" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="H103" s="41"/>
+      <c r="I103" s="41"/>
+      <c r="J103" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="K103" s="41"/>
+      <c r="L103" s="41"/>
+      <c r="M103" s="41"/>
+    </row>
+    <row r="104" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B104" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="C104" s="42"/>
+      <c r="D104" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="E104" s="41"/>
+      <c r="F104" s="41"/>
+      <c r="G104" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="H104" s="41"/>
+      <c r="I104" s="41"/>
+      <c r="J104" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="K104" s="43"/>
+      <c r="L104" s="43"/>
+      <c r="M104" s="43"/>
+    </row>
+    <row r="105" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B105" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="C105" s="42"/>
+      <c r="D105" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="E105" s="41"/>
+      <c r="F105" s="41"/>
+      <c r="G105" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="H105" s="41"/>
+      <c r="I105" s="41"/>
+      <c r="J105" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="K105" s="43"/>
+      <c r="L105" s="43"/>
+      <c r="M105" s="43"/>
+    </row>
+    <row r="107" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B107" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C107" s="31"/>
+      <c r="D107" s="31"/>
+      <c r="E107" s="31"/>
+      <c r="F107" s="31"/>
+      <c r="G107" s="31"/>
+      <c r="H107" s="31"/>
+      <c r="I107" s="31"/>
+      <c r="J107" s="31"/>
+      <c r="K107" s="31"/>
+      <c r="L107" s="31"/>
+      <c r="M107" s="31"/>
+    </row>
+    <row r="108" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B108" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="C108" s="44"/>
+      <c r="D108" s="44"/>
+      <c r="E108" s="44"/>
+      <c r="F108" s="44"/>
+      <c r="G108" s="44"/>
+      <c r="H108" s="44"/>
+      <c r="I108" s="44"/>
+      <c r="J108" s="44"/>
+      <c r="K108" s="44"/>
+      <c r="L108" s="44"/>
+      <c r="M108" s="44"/>
+    </row>
+    <row r="110" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B110" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B111" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+    </row>
+    <row r="112" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B112" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C99" s="13"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="14" t="s">
+      <c r="C112" s="13"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
-      <c r="H99" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="L99" s="14"/>
-      <c r="M99" s="14"/>
-    </row>
-    <row r="100" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B100" s="8" t="n">
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
+      <c r="H112" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
+      <c r="K112" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L112" s="14"/>
+      <c r="M112" s="14"/>
+    </row>
+    <row r="113" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B113" s="8" t="n">
         <f aca="false">SUMIF('AB玉 増減明細'!$A$4:$A$26,"建築",'AB玉 増減明細'!$E$4:$E$26)</f>
         <v>462</v>
       </c>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="29" t="n">
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="29" t="n">
         <f aca="false">SUMIF('CD玉 増減明細'!$A$4:$A$23,"建築",'CD玉 増減明細'!$E$4:$E$23)</f>
         <v>0</v>
       </c>
-      <c r="F100" s="29"/>
-      <c r="G100" s="29"/>
-      <c r="H100" s="36" t="n">
+      <c r="F113" s="29"/>
+      <c r="G113" s="29"/>
+      <c r="H113" s="45" t="n">
         <f aca="false">SUMIF(成約明細!$A$4:$A$22,"建築",成約明細!$C$4:$C$22)</f>
         <v>535</v>
       </c>
-      <c r="I100" s="36"/>
-      <c r="J100" s="36"/>
-      <c r="K100" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="L100" s="37"/>
-      <c r="M100" s="37"/>
-    </row>
-    <row r="101" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B101" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C101" s="19"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F101" s="20"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I101" s="11"/>
-      <c r="J101" s="11"/>
-      <c r="K101" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="L101" s="20"/>
-      <c r="M101" s="20"/>
-    </row>
-    <row r="103" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B103" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B104" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="4"/>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
-    </row>
-    <row r="105" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B105" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C105" s="38"/>
-      <c r="D105" s="38"/>
-      <c r="E105" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F105" s="38"/>
-      <c r="G105" s="38"/>
-      <c r="H105" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="I105" s="38"/>
-      <c r="J105" s="38"/>
-      <c r="K105" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="L105" s="38"/>
-      <c r="M105" s="38"/>
-    </row>
-    <row r="106" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B106" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="C106" s="39"/>
-      <c r="D106" s="39"/>
-      <c r="E106" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="F106" s="39"/>
-      <c r="G106" s="39"/>
-      <c r="H106" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="I106" s="40"/>
-      <c r="J106" s="40"/>
-      <c r="K106" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="L106" s="39"/>
-      <c r="M106" s="39"/>
-    </row>
-    <row r="107" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B107" s="39"/>
-      <c r="C107" s="39"/>
-      <c r="D107" s="39"/>
-      <c r="E107" s="39"/>
-      <c r="F107" s="39"/>
-      <c r="G107" s="39"/>
-      <c r="H107" s="40"/>
-      <c r="I107" s="40"/>
-      <c r="J107" s="40"/>
-      <c r="K107" s="39"/>
-      <c r="L107" s="39"/>
-      <c r="M107" s="39"/>
+      <c r="I113" s="45"/>
+      <c r="J113" s="45"/>
+      <c r="K113" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="L113" s="46"/>
+      <c r="M113" s="46"/>
+    </row>
+    <row r="114" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B114" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C114" s="19"/>
+      <c r="D114" s="19"/>
+      <c r="E114" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F114" s="20"/>
+      <c r="G114" s="20"/>
+      <c r="H114" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I114" s="11"/>
+      <c r="J114" s="11"/>
+      <c r="K114" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L114" s="20"/>
+      <c r="M114" s="20"/>
+    </row>
+    <row r="116" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B116" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3"/>
+      <c r="L116" s="3"/>
+      <c r="M116" s="3"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B117" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+    </row>
+    <row r="118" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B118" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C118" s="47"/>
+      <c r="D118" s="47"/>
+      <c r="E118" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="F118" s="47"/>
+      <c r="G118" s="47"/>
+      <c r="H118" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="I118" s="47"/>
+      <c r="J118" s="47"/>
+      <c r="K118" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="L118" s="47"/>
+      <c r="M118" s="47"/>
+    </row>
+    <row r="119" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B119" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C119" s="48"/>
+      <c r="D119" s="48"/>
+      <c r="E119" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="F119" s="48"/>
+      <c r="G119" s="48"/>
+      <c r="H119" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I119" s="49"/>
+      <c r="J119" s="49"/>
+      <c r="K119" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="L119" s="48"/>
+      <c r="M119" s="48"/>
+    </row>
+    <row r="120" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B120" s="48"/>
+      <c r="C120" s="48"/>
+      <c r="D120" s="48"/>
+      <c r="E120" s="48"/>
+      <c r="F120" s="48"/>
+      <c r="G120" s="48"/>
+      <c r="H120" s="49"/>
+      <c r="I120" s="49"/>
+      <c r="J120" s="49"/>
+      <c r="K120" s="48"/>
+      <c r="L120" s="48"/>
+      <c r="M120" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="132">
+  <mergeCells count="164">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="B5:M5"/>
@@ -10620,28 +12883,60 @@
     <mergeCell ref="K95:M95"/>
     <mergeCell ref="B97:M97"/>
     <mergeCell ref="B98:M98"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="H99:J99"/>
-    <mergeCell ref="K99:M99"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="H100:J100"/>
-    <mergeCell ref="K100:M100"/>
-    <mergeCell ref="B101:D101"/>
-    <mergeCell ref="E101:G101"/>
-    <mergeCell ref="H101:J101"/>
-    <mergeCell ref="K101:M101"/>
-    <mergeCell ref="B103:M103"/>
-    <mergeCell ref="B104:M104"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="E105:G105"/>
-    <mergeCell ref="H105:J105"/>
-    <mergeCell ref="K105:M105"/>
-    <mergeCell ref="B106:D107"/>
-    <mergeCell ref="E106:G107"/>
-    <mergeCell ref="H106:J107"/>
-    <mergeCell ref="K106:M107"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="G99:I99"/>
+    <mergeCell ref="J99:M99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="J100:M100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="G101:I101"/>
+    <mergeCell ref="J101:M101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="G102:I102"/>
+    <mergeCell ref="J102:M102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="G103:I103"/>
+    <mergeCell ref="J103:M103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="G104:I104"/>
+    <mergeCell ref="J104:M104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="G105:I105"/>
+    <mergeCell ref="J105:M105"/>
+    <mergeCell ref="B107:M107"/>
+    <mergeCell ref="B108:M108"/>
+    <mergeCell ref="B110:M110"/>
+    <mergeCell ref="B111:M111"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="E112:G112"/>
+    <mergeCell ref="H112:J112"/>
+    <mergeCell ref="K112:M112"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="K113:M113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="E114:G114"/>
+    <mergeCell ref="H114:J114"/>
+    <mergeCell ref="K114:M114"/>
+    <mergeCell ref="B116:M116"/>
+    <mergeCell ref="B117:M117"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="E118:G118"/>
+    <mergeCell ref="H118:J118"/>
+    <mergeCell ref="K118:M118"/>
+    <mergeCell ref="B119:D120"/>
+    <mergeCell ref="E119:G120"/>
+    <mergeCell ref="H119:J120"/>
+    <mergeCell ref="K119:M120"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10689,637 +12984,637 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="51" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="55" t="n">
+        <v>7616</v>
+      </c>
+      <c r="E4" s="56" t="n">
+        <v>7616</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="59" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E5" s="60" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F5" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>1128</v>
+      </c>
+      <c r="E6" s="56" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="59" t="n">
+        <v>545</v>
+      </c>
+      <c r="E7" s="60" t="n">
+        <v>545</v>
+      </c>
+      <c r="F7" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>462</v>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>462</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="59" t="n">
+        <v>430</v>
+      </c>
+      <c r="E9" s="60" t="n">
+        <v>430</v>
+      </c>
+      <c r="F9" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>265</v>
+      </c>
+      <c r="E10" s="56" t="n">
+        <v>265</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>220</v>
+      </c>
+      <c r="E11" s="60" t="n">
+        <v>220</v>
+      </c>
+      <c r="F11" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>173</v>
+      </c>
+      <c r="E12" s="56" t="n">
+        <v>173</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>150</v>
+      </c>
+      <c r="E13" s="60" t="n">
+        <v>150</v>
+      </c>
+      <c r="F13" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="55" t="n">
+        <v>149</v>
+      </c>
+      <c r="E14" s="56" t="n">
+        <v>149</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>120</v>
+      </c>
+      <c r="E15" s="60" t="n">
+        <v>120</v>
+      </c>
+      <c r="F15" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="55" t="n">
+        <v>98</v>
+      </c>
+      <c r="E16" s="56" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="E17" s="60" t="n">
+        <v>70</v>
+      </c>
+      <c r="F17" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="55" t="n">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="44" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="46" t="n">
+      <c r="E18" s="56" t="n">
+        <v>62</v>
+      </c>
+      <c r="F18" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="46" t="n">
-        <v>7616</v>
-      </c>
-      <c r="E4" s="47" t="n">
-        <v>7616</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="48" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="50" t="n">
+      <c r="D19" s="59" t="n">
+        <v>62</v>
+      </c>
+      <c r="E19" s="60" t="n">
+        <v>62</v>
+      </c>
+      <c r="F19" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="50" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E5" s="51" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F5" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="46" t="n">
+      <c r="D20" s="55" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" s="56" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="59" t="n">
+        <v>1570</v>
+      </c>
+      <c r="D21" s="59" t="n">
+        <v>1616</v>
+      </c>
+      <c r="E21" s="60" t="n">
+        <v>46</v>
+      </c>
+      <c r="F21" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="46" t="n">
-        <v>1128</v>
-      </c>
-      <c r="E6" s="47" t="n">
-        <v>1128</v>
-      </c>
-      <c r="F6" s="45" t="s">
+      <c r="D22" s="55" t="n">
+        <v>38</v>
+      </c>
+      <c r="E22" s="56" t="n">
+        <v>38</v>
+      </c>
+      <c r="F22" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="50" t="n">
+      <c r="G22" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="50" t="n">
-        <v>545</v>
-      </c>
-      <c r="E7" s="51" t="n">
-        <v>545</v>
-      </c>
-      <c r="F7" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="46" t="n">
+      <c r="D23" s="59" t="n">
+        <v>37</v>
+      </c>
+      <c r="E23" s="60" t="n">
+        <v>37</v>
+      </c>
+      <c r="F23" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="46" t="n">
-        <v>462</v>
-      </c>
-      <c r="E8" s="47" t="n">
-        <v>462</v>
-      </c>
-      <c r="F8" s="45" t="s">
+      <c r="D24" s="55" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="50" t="n">
+      <c r="G24" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="50" t="n">
-        <v>430</v>
-      </c>
-      <c r="E9" s="51" t="n">
-        <v>430</v>
-      </c>
-      <c r="F9" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>265</v>
-      </c>
-      <c r="E10" s="47" t="n">
-        <v>265</v>
-      </c>
-      <c r="F10" s="45" t="s">
+      <c r="D25" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="50" t="n">
-        <v>220</v>
-      </c>
-      <c r="E11" s="51" t="n">
-        <v>220</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="52" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="46" t="n">
-        <v>173</v>
-      </c>
-      <c r="E12" s="47" t="n">
-        <v>173</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="50" t="n">
-        <v>150</v>
-      </c>
-      <c r="E13" s="51" t="n">
-        <v>150</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="46" t="n">
-        <v>149</v>
-      </c>
-      <c r="E14" s="47" t="n">
-        <v>149</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="50" t="n">
-        <v>120</v>
-      </c>
-      <c r="E15" s="51" t="n">
-        <v>120</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="46" t="n">
-        <v>98</v>
-      </c>
-      <c r="E16" s="47" t="n">
-        <v>98</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>70</v>
-      </c>
-      <c r="E17" s="51" t="n">
-        <v>70</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="46" t="n">
-        <v>62</v>
-      </c>
-      <c r="E18" s="47" t="n">
-        <v>62</v>
-      </c>
-      <c r="F18" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="50" t="n">
-        <v>62</v>
-      </c>
-      <c r="E19" s="51" t="n">
-        <v>62</v>
-      </c>
-      <c r="F19" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H19" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="46" t="n">
-        <v>50</v>
-      </c>
-      <c r="E20" s="47" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="50" t="n">
-        <v>1570</v>
-      </c>
-      <c r="D21" s="50" t="n">
-        <v>1616</v>
-      </c>
-      <c r="E21" s="51" t="n">
-        <v>46</v>
-      </c>
-      <c r="F21" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="46" t="n">
-        <v>38</v>
-      </c>
-      <c r="E22" s="47" t="n">
-        <v>38</v>
-      </c>
-      <c r="F22" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H22" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="50" t="n">
-        <v>37</v>
-      </c>
-      <c r="E23" s="51" t="n">
-        <v>37</v>
-      </c>
-      <c r="F23" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="E24" s="47" t="n">
-        <v>12</v>
-      </c>
-      <c r="F24" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" s="51" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H25" s="52" t="s">
-        <v>77</v>
+      <c r="G25" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="46" t="n">
+      <c r="A26" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="55" t="n">
         <v>2000</v>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="55" t="n">
         <v>1950</v>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="56" t="n">
         <v>-50</v>
       </c>
-      <c r="F26" s="45" t="s">
+      <c r="F26" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="48" t="s">
-        <v>77</v>
+      <c r="G26" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" s="57" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -11350,559 +13645,559 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="51" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="53" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="54" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="44" t="s">
+      <c r="B4" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="55" t="n">
+        <v>5834</v>
+      </c>
+      <c r="E4" s="56" t="n">
+        <v>5834</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="59" t="n">
+        <v>1649</v>
+      </c>
+      <c r="E5" s="60" t="n">
+        <v>1649</v>
+      </c>
+      <c r="F5" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="61" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E6" s="56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="59" t="n">
+        <v>390</v>
+      </c>
+      <c r="E7" s="60" t="n">
+        <v>390</v>
+      </c>
+      <c r="F7" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>360</v>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>360</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>920</v>
+      </c>
+      <c r="D9" s="59" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E9" s="60" t="n">
+        <v>330</v>
+      </c>
+      <c r="F9" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>235</v>
+      </c>
+      <c r="E10" s="56" t="n">
+        <v>235</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>120</v>
+      </c>
+      <c r="E11" s="60" t="n">
+        <v>120</v>
+      </c>
+      <c r="F11" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" s="56" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>106</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="60" t="n">
+        <v>-106</v>
+      </c>
+      <c r="F13" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="55" t="n">
+        <v>140</v>
+      </c>
+      <c r="D14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="56" t="n">
+        <v>-140</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="59" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="60" t="n">
+        <v>-300</v>
+      </c>
+      <c r="F15" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="55" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="56" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>785</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="60" t="n">
+        <v>-785</v>
+      </c>
+      <c r="F17" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="61" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="55" t="n">
+        <v>800</v>
+      </c>
+      <c r="D18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="56" t="n">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="C19" s="59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="60" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F19" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="44" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="45" t="s">
+      <c r="G19" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="46" t="n">
+      <c r="H19" s="61" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="46" t="n">
-        <v>5834</v>
-      </c>
-      <c r="E4" s="47" t="n">
-        <v>5834</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="50" t="n">
+      <c r="E20" s="56" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="59" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D21" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="50" t="n">
-        <v>1649</v>
-      </c>
-      <c r="E5" s="51" t="n">
-        <v>1649</v>
-      </c>
-      <c r="F5" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="45" t="s">
+      <c r="E21" s="60" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="F21" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="61" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="55" t="n">
+        <v>1572</v>
+      </c>
+      <c r="D22" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="56" t="n">
+        <v>-1572</v>
+      </c>
+      <c r="F22" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" s="57" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="46" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E6" s="47" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="49" t="s">
+      <c r="C23" s="59" t="n">
+        <v>3352</v>
+      </c>
+      <c r="D23" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="60" t="n">
+        <v>-3352</v>
+      </c>
+      <c r="F23" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="61" t="s">
         <v>109</v>
-      </c>
-      <c r="C7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="50" t="n">
-        <v>390</v>
-      </c>
-      <c r="E7" s="51" t="n">
-        <v>390</v>
-      </c>
-      <c r="F7" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="46" t="n">
-        <v>360</v>
-      </c>
-      <c r="E8" s="47" t="n">
-        <v>360</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="50" t="n">
-        <v>920</v>
-      </c>
-      <c r="D9" s="50" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E9" s="51" t="n">
-        <v>330</v>
-      </c>
-      <c r="F9" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>235</v>
-      </c>
-      <c r="E10" s="47" t="n">
-        <v>235</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="50" t="n">
-        <v>120</v>
-      </c>
-      <c r="E11" s="51" t="n">
-        <v>120</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="E12" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="50" t="n">
-        <v>106</v>
-      </c>
-      <c r="D13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="51" t="n">
-        <v>-106</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="46" t="n">
-        <v>140</v>
-      </c>
-      <c r="D14" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="47" t="n">
-        <v>-140</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="50" t="n">
-        <v>300</v>
-      </c>
-      <c r="D15" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="51" t="n">
-        <v>-300</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="D16" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="47" t="n">
-        <v>-500</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>785</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="51" t="n">
-        <v>-785</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="46" t="n">
-        <v>800</v>
-      </c>
-      <c r="D18" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="47" t="n">
-        <v>-800</v>
-      </c>
-      <c r="F18" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D19" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="51" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="F19" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="52" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D20" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="47" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="F20" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="50" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D21" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="51" t="n">
-        <v>-1300</v>
-      </c>
-      <c r="F21" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21" s="52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22" s="46" t="n">
-        <v>1572</v>
-      </c>
-      <c r="D22" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="47" t="n">
-        <v>-1572</v>
-      </c>
-      <c r="F22" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="H22" s="48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="50" t="n">
-        <v>3352</v>
-      </c>
-      <c r="D23" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="51" t="n">
-        <v>-3352</v>
-      </c>
-      <c r="F23" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="52" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -11932,353 +14227,353 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="62" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="55" t="n">
+        <v>3640</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="61" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" s="61" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="55" t="n">
+        <v>1475</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>1384</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="55" t="n">
+        <v>535</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>430</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="55" t="n">
+        <v>265</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>173</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="55" t="n">
+        <v>150</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="58" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="53" t="s">
+      <c r="C15" s="59" t="n">
+        <v>149</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="54" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="43" t="s">
+      <c r="C16" s="55" t="n">
+        <v>120</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="C17" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" s="61" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="54" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="45" t="s">
+      <c r="C18" s="55" t="n">
+        <v>62</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="46" t="n">
-        <v>3640</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="50" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D5" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="52" t="s">
+      <c r="C19" s="59" t="n">
+        <v>62</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="61" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="54" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="46" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D6" s="48" t="s">
+      <c r="C20" s="55" t="n">
+        <v>38</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" s="57" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="C21" s="59" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" s="61" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="54" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="50" t="n">
-        <v>1950</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="46" t="n">
-        <v>1475</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="50" t="n">
-        <v>1384</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="46" t="n">
-        <v>535</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="50" t="n">
-        <v>430</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="52" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="46" t="n">
-        <v>265</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="50" t="n">
-        <v>173</v>
-      </c>
-      <c r="D13" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="46" t="n">
-        <v>150</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="50" t="n">
-        <v>149</v>
-      </c>
-      <c r="D15" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" s="52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="46" t="n">
-        <v>120</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>70</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="52" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="46" t="n">
-        <v>62</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" s="48" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="50" t="n">
-        <v>62</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" s="52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="46" t="n">
-        <v>38</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="50" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" s="52" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="46" t="n">
+      <c r="C22" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>147</v>
+      <c r="D22" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -12309,868 +14604,868 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
-        <v>148</v>
+      <c r="A1" s="50" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="62" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="55" t="n">
+        <v>5834</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="54"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="G5" s="58"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="G6" s="54"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>462</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="G7" s="58"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="55" t="n">
+        <v>360</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="G8" s="54"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>265</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="58"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="55" t="n">
+        <v>235</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="G10" s="54"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>173</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="G11" s="58"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="55" t="n">
         <v>149</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="43" t="s">
+      <c r="D12" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" s="54"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>120</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="G13" s="58"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="55" t="n">
+        <v>120</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="G14" s="54"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="43" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="45" t="s">
+      <c r="C15" s="59" t="n">
+        <v>98</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="G15" s="58"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="55" t="n">
+        <v>80</v>
+      </c>
+      <c r="D16" s="57" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="46" t="n">
-        <v>5834</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="48" t="s">
+      <c r="E16" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="G16" s="54"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>62</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="F17" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="G17" s="58"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="55" t="n">
+        <v>62</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="G18" s="54"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" s="58"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="48" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="45"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="50" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D5" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="G5" s="49"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="46" t="n">
-        <v>1128</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="45"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="50" t="n">
-        <v>462</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F7" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="49"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="46" t="n">
-        <v>360</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>154</v>
-      </c>
-      <c r="G8" s="45"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="50" t="n">
-        <v>265</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="52" t="s">
+      <c r="C20" s="55" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="G20" s="54"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="59" t="n">
+        <v>38</v>
+      </c>
+      <c r="D21" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="G21" s="58"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" s="55" t="n">
+        <v>37</v>
+      </c>
+      <c r="D22" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="G22" s="54"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="59" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="F23" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="G23" s="58"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="G24" s="54"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="F9" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="G9" s="49"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="46" t="n">
-        <v>235</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="G10" s="45"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="50" t="n">
-        <v>173</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="52" t="s">
+      <c r="F25" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>199</v>
+      </c>
+      <c r="C26" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="G11" s="49"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="46" t="n">
-        <v>149</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="48" t="s">
+      <c r="F26" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="G26" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="F12" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="G12" s="45"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="50" t="n">
-        <v>120</v>
-      </c>
-      <c r="D13" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F13" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" s="49"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="46" t="n">
-        <v>120</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="48" t="s">
+      <c r="F27" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="F14" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" s="45"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="50" t="n">
-        <v>98</v>
-      </c>
-      <c r="D15" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="52" t="s">
+      <c r="F28" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="G28" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="F15" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="G15" s="49"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="46" t="n">
-        <v>80</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>154</v>
-      </c>
-      <c r="G16" s="45"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>62</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="52" t="s">
+      <c r="F29" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="F17" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="G17" s="49"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="46" t="n">
-        <v>62</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="48" t="s">
+      <c r="F30" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C31" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="F18" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="G18" s="45"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="C19" s="50" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="F19" s="52" t="s">
-        <v>163</v>
-      </c>
-      <c r="G19" s="49"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="46" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="48" t="s">
+      <c r="F31" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="G20" s="45"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="50" t="n">
-        <v>38</v>
-      </c>
-      <c r="D21" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="52" t="s">
+      <c r="F32" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="G32" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="58" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="F21" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="G21" s="49"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" s="46" t="n">
-        <v>37</v>
-      </c>
-      <c r="D22" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="G22" s="45"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="50" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="52" t="s">
+      <c r="F33" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="G33" s="61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="F23" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="G23" s="49"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="D24" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="48" t="s">
+      <c r="F34" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="G34" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="F24" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="G24" s="45"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" s="50" t="n">
+      <c r="F35" s="61" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" s="61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F25" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="G25" s="52" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="C26" s="46" t="n">
+      <c r="D36" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F36" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="G26" s="48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>169</v>
-      </c>
-      <c r="C27" s="50" t="n">
+      <c r="D37" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="G37" s="61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F27" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="G27" s="52" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="C28" s="46" t="n">
+      <c r="D38" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F38" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="G38" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="C39" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="G28" s="48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="C29" s="50" t="n">
+      <c r="D39" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="54" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F29" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="G29" s="52" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="46" t="n">
+      <c r="D40" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="G40" s="57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F30" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="G30" s="48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="C31" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="E31" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F31" s="52" t="s">
-        <v>177</v>
-      </c>
-      <c r="G31" s="52" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="C32" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E32" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="G32" s="48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="49" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F33" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="G33" s="52" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="C34" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E34" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F34" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="G34" s="48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="C35" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F35" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="G35" s="52" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F36" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="G36" s="48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="C37" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F37" s="52" t="s">
-        <v>185</v>
-      </c>
-      <c r="G37" s="52" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="C38" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F38" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="G38" s="48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="C39" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="F39" s="52" t="s">
-        <v>154</v>
-      </c>
-      <c r="G39" s="52" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="C40" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E40" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F40" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="G40" s="48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B41" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="C41" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="E41" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F41" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="G41" s="52" t="s">
-        <v>166</v>
+      <c r="D41" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="G41" s="61" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -13200,183 +15495,183 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
-        <v>191</v>
+      <c r="A1" s="50" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="53" t="s">
-        <v>192</v>
+      <c r="A2" s="62" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="43" t="s">
+      <c r="A3" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="55" t="n">
+        <v>1572</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="61" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="E3" s="43" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="46" t="n">
-        <v>1572</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="50" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D5" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="52" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="46" t="n">
+      <c r="C6" s="55" t="n">
         <v>1000</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>188</v>
+      <c r="D6" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="50" t="n">
+      <c r="A7" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="59" t="n">
         <v>800</v>
       </c>
-      <c r="D7" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>127</v>
+      <c r="D7" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="61" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="46" t="n">
+      <c r="A8" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="55" t="n">
         <v>785</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>127</v>
+      <c r="D8" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="50" t="n">
+      <c r="A9" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="59" t="n">
         <v>140</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>140</v>
+      <c r="D9" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="46" t="n">
+      <c r="A10" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>127</v>
+      <c r="D10" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="50" t="n">
+      <c r="A11" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="52" t="s">
-        <v>188</v>
+      <c r="D11" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="46" t="n">
+      <c r="A12" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>127</v>
+      <c r="D12" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -13403,183 +15698,183 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="54" t="s">
-        <v>197</v>
+      <c r="A1" s="63" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="53" t="s">
-        <v>198</v>
+      <c r="A2" s="62" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="55" t="s">
-        <v>199</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>202</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>203</v>
+      <c r="A4" s="64" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="B5" s="58" t="n">
+      <c r="A5" s="66" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" s="67" t="n">
         <f aca="false">B6-SUMIF('AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON",'AB玉 増減明細'!$E$4:$E$26)</f>
         <v>85087</v>
       </c>
-      <c r="C5" s="58" t="n">
+      <c r="C5" s="67" t="n">
         <f aca="false">C6-SUMIF('CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON",'CD玉 増減明細'!$E$4:$E$23)</f>
         <v>184157</v>
       </c>
-      <c r="D5" s="59" t="n">
+      <c r="D5" s="68" t="n">
         <v>300</v>
       </c>
-      <c r="E5" s="60" t="n">
+      <c r="E5" s="69" t="n">
         <f aca="false">SUM(B5:D5)</f>
         <v>269544</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" s="59" t="n">
+      <c r="A6" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="68" t="n">
         <v>99318</v>
       </c>
-      <c r="C6" s="59" t="n">
+      <c r="C6" s="68" t="n">
         <v>183800</v>
       </c>
-      <c r="D6" s="59" t="n">
+      <c r="D6" s="68" t="n">
         <v>300</v>
       </c>
-      <c r="E6" s="60" t="n">
+      <c r="E6" s="69" t="n">
         <f aca="false">SUM(B6:D6)</f>
         <v>283418</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="62" t="n">
+      <c r="B7" s="71" t="n">
         <f aca="false">B6-B5</f>
         <v>14231</v>
       </c>
-      <c r="C7" s="62" t="n">
+      <c r="C7" s="71" t="n">
         <f aca="false">C6-C5</f>
         <v>-357</v>
       </c>
-      <c r="D7" s="62" t="n">
+      <c r="D7" s="71" t="n">
         <f aca="false">D6-D5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="62" t="n">
+      <c r="E7" s="71" t="n">
         <f aca="false">E6-E5</f>
         <v>13874</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="63" t="s">
-        <v>206</v>
+      <c r="A9" s="72" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="58" t="n">
+      <c r="A10" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="67" t="n">
         <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"確度UP（CD→AB）",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>11811</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="58" t="n">
+      <c r="B11" s="67" t="n">
         <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"新規作成",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>2204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B12" s="58" t="n">
+      <c r="A12" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="B12" s="67" t="n">
         <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"失注から復活",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")+SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"増額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="64" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="65" t="n">
+      <c r="A13" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="B13" s="74" t="n">
         <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"減額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>-50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63" t="s">
-        <v>209</v>
+      <c r="A16" s="72" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="58" t="n">
+      <c r="B17" s="67" t="n">
         <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"新規作成",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
         <v>6629</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="58" t="n">
+      <c r="B18" s="67" t="n">
         <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"増額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
         <v>3869</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="66" t="s">
-        <v>210</v>
+      <c r="A20" s="75" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="58" t="n">
+      <c r="B21" s="67" t="n">
         <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"失注",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
         <v>5597</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="B22" s="58" t="n">
+      <c r="A22" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="B22" s="67" t="n">
         <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"確度UP（CD→AB）",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
         <v>5258</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="58" t="n">
+      <c r="B23" s="67" t="n">
         <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"減額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
         <v>0</v>
       </c>
@@ -13608,206 +15903,206 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="54" t="s">
-        <v>212</v>
+      <c r="A1" s="63" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="67" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" s="68"/>
+      <c r="A3" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="77"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="s">
-        <v>214</v>
-      </c>
-      <c r="B4" s="70" t="s">
-        <v>215</v>
+      <c r="A4" s="78" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="79" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>217</v>
+      <c r="A5" s="78" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" s="77" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="69" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" s="70" t="s">
-        <v>219</v>
+      <c r="A6" s="78" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" s="79" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71"/>
-      <c r="B7" s="70"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="79"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="67" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="70"/>
+      <c r="A8" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="79"/>
     </row>
     <row r="9" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="72" t="s">
-        <v>221</v>
-      </c>
-      <c r="B9" s="68" t="s">
-        <v>222</v>
+      <c r="A9" s="81" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="72" t="s">
-        <v>223</v>
-      </c>
-      <c r="B10" s="70" t="s">
-        <v>224</v>
+      <c r="A10" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="B10" s="79" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="72" t="s">
-        <v>225</v>
-      </c>
-      <c r="B11" s="70" t="s">
-        <v>226</v>
+      <c r="A11" s="81" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="79" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="69" t="s">
-        <v>202</v>
-      </c>
-      <c r="B12" s="70" t="s">
-        <v>227</v>
+      <c r="A12" s="78" t="s">
+        <v>234</v>
+      </c>
+      <c r="B12" s="79" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="69" t="s">
-        <v>228</v>
-      </c>
-      <c r="B13" s="68" t="s">
-        <v>229</v>
+      <c r="A13" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71"/>
-      <c r="B14" s="70"/>
+      <c r="A14" s="80"/>
+      <c r="B14" s="79"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="67" t="s">
-        <v>230</v>
-      </c>
-      <c r="B15" s="70"/>
+      <c r="A15" s="76" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="79"/>
     </row>
     <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="72" t="s">
-        <v>231</v>
-      </c>
-      <c r="B16" s="68" t="s">
-        <v>232</v>
+      <c r="A16" s="81" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="77" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="72" t="s">
-        <v>233</v>
-      </c>
-      <c r="B17" s="68" t="s">
-        <v>234</v>
+      <c r="A17" s="81" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" s="77" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="72" t="s">
-        <v>235</v>
-      </c>
-      <c r="B18" s="68" t="s">
-        <v>236</v>
+      <c r="A18" s="81" t="s">
+        <v>267</v>
+      </c>
+      <c r="B18" s="77" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="s">
-        <v>237</v>
-      </c>
-      <c r="B19" s="70" t="s">
-        <v>238</v>
+      <c r="A19" s="81" t="s">
+        <v>269</v>
+      </c>
+      <c r="B19" s="79" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="69" t="s">
-        <v>239</v>
-      </c>
-      <c r="B20" s="68" t="s">
-        <v>240</v>
+      <c r="A20" s="78" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="77" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71"/>
-      <c r="B21" s="70"/>
+      <c r="A21" s="80"/>
+      <c r="B21" s="79"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="67" t="s">
-        <v>241</v>
-      </c>
-      <c r="B22" s="70"/>
+      <c r="A22" s="76" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" s="79"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="69" t="s">
-        <v>242</v>
-      </c>
-      <c r="B23" s="70" t="s">
-        <v>243</v>
+      <c r="A23" s="78" t="s">
+        <v>274</v>
+      </c>
+      <c r="B23" s="79" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="B24" s="70" t="s">
-        <v>245</v>
+      <c r="A24" s="78" t="s">
+        <v>276</v>
+      </c>
+      <c r="B24" s="79" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71"/>
-      <c r="B25" s="70"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="79"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="67" t="s">
-        <v>246</v>
-      </c>
-      <c r="B26" s="70"/>
+      <c r="A26" s="76" t="s">
+        <v>278</v>
+      </c>
+      <c r="B26" s="79"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="69" t="s">
-        <v>247</v>
-      </c>
-      <c r="B27" s="70" t="s">
-        <v>248</v>
+      <c r="A27" s="78" t="s">
+        <v>279</v>
+      </c>
+      <c r="B27" s="79" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="69" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="70" t="s">
-        <v>249</v>
+      <c r="A28" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="B28" s="79" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="69" t="s">
-        <v>250</v>
-      </c>
-      <c r="B29" s="70" t="s">
-        <v>251</v>
+      <c r="A29" s="78" t="s">
+        <v>282</v>
+      </c>
+      <c r="B29" s="79" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="72" t="s">
-        <v>252</v>
-      </c>
-      <c r="B30" s="68" t="s">
-        <v>253</v>
+      <c r="A30" s="81" t="s">
+        <v>284</v>
+      </c>
+      <c r="B30" s="77" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/9月振り返り_コーデTB建築.xlsx
+++ b/9月振り返り_コーデTB建築.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="263">
   <si>
     <r>
       <rPr>
@@ -1632,49 +1632,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">④　</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月の動き</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">成約・新規作成・失注。明細は各シートにあります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成約</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新規のうち金額未入力</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⑤　今月のトピック</t>
+    <t xml:space="preserve">④　今月のトピック</t>
   </si>
   <si>
     <r>
@@ -3625,377 +3583,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">が別途あります。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⑥　建築</t>
-  </si>
-  <si>
-    <t xml:space="preserve">建築案件は通期スナップショットのレポートが未取得のため、増減のみ表示しています。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月の成約</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末の絶対値</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">未取得</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">枠材製作（材工）モックアップ製作 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">動きなし</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CLT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">試験材 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">★建築</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">総商談</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF767676"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通期 のレポートがあれば出せます</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⑦　来月に向けて</t>
-  </si>
-  <si>
-    <t xml:space="preserve">この振り返りから出てくる打ち手です。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">①</t>
-  </si>
-  <si>
-    <t xml:space="preserve">②</t>
-  </si>
-  <si>
-    <t xml:space="preserve">③</t>
-  </si>
-  <si>
-    <t xml:space="preserve">④</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新規</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">38</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件のうち金額未入力</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件を埋める</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">認証桧柾目材・千本松牧場に続く案件を特定する</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CD</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">玉のストックを増やす（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月は </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-357</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">建築の玉が</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FF2C5F2D"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件のみ。増やす手を打つ</t>
     </r>
   </si>
   <si>
@@ -9061,7 +8648,7 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="56">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9281,14 +8868,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="24"/>
-      <color rgb="FFB04A3C"/>
-      <name val="Meiryo"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="9.5"/>
       <color rgb="FFFFFFFF"/>
       <name val="WenQuanYi Zen Hei"/>
@@ -9341,28 +8920,6 @@
       <color rgb="FF2C5F2D"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10.5"/>
-      <color rgb="FF2C5F2D"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10.5"/>
-      <color rgb="FF2C5F2D"/>
-      <name val="Meiryo"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -9627,7 +9184,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9756,24 +9313,12 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="30" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="30" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -9784,7 +9329,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9792,15 +9341,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9808,27 +9349,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9836,15 +9357,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9852,31 +9425,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="50" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="50" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9884,63 +9461,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="52" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="55" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="58" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9948,11 +9473,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10333,11 +9854,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="70636339"/>
-        <c:axId val="72114459"/>
+        <c:axId val="17896400"/>
+        <c:axId val="93625095"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70636339"/>
+        <c:axId val="17896400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10369,7 +9890,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72114459"/>
+        <c:crossAx val="93625095"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10377,7 +9898,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72114459"/>
+        <c:axId val="93625095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10409,7 +9930,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70636339"/>
+        <c:crossAx val="17896400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11546,7 +11067,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:M120"/>
+  <dimension ref="B2:M102"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.2"/>
@@ -12288,491 +11809,194 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
     </row>
-    <row r="93" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="6" t="s">
+    <row r="93" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B93" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="I93" s="22"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="22" t="s">
+      <c r="C93" s="32"/>
+      <c r="D93" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="L93" s="22"/>
-      <c r="M93" s="22"/>
-    </row>
-    <row r="94" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="32" t="n">
-        <f aca="false">SUM(成約明細!$C$4:$C$22)</f>
-        <v>16525</v>
-      </c>
-      <c r="C94" s="32"/>
-      <c r="D94" s="32"/>
-      <c r="E94" s="33" t="n">
-        <f aca="false">SUM(新規作成明細!$C$4:$C$41)</f>
-        <v>10865</v>
-      </c>
-      <c r="F94" s="33"/>
-      <c r="G94" s="33"/>
-      <c r="H94" s="34" t="n">
-        <f aca="false">-SUM(失注明細!$C$4:$C$12)</f>
-        <v>-5597</v>
-      </c>
-      <c r="I94" s="34"/>
-      <c r="J94" s="34"/>
-      <c r="K94" s="35" t="n">
-        <f aca="false">COUNTIF(新規作成明細!$G$4:$G$41,"●")</f>
-        <v>17</v>
-      </c>
-      <c r="L94" s="35"/>
-      <c r="M94" s="35"/>
-    </row>
-    <row r="95" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B95" s="11" t="str">
-        <f aca="false">19&amp;"件"</f>
-        <v>19件</v>
-      </c>
-      <c r="C95" s="11"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="26" t="str">
-        <f aca="false">38&amp;"件"</f>
-        <v>38件</v>
-      </c>
-      <c r="F95" s="26"/>
-      <c r="G95" s="26"/>
-      <c r="H95" s="27" t="str">
-        <f aca="false">9&amp;"件。すべて確度C・D"</f>
-        <v>9件。すべて確度C・D</v>
-      </c>
-      <c r="I95" s="27"/>
-      <c r="J95" s="27"/>
-      <c r="K95" s="27" t="str">
-        <f aca="false">"件。新規"&amp;38&amp;"件の"&amp;TEXT(COUNTIF(新規作成明細!$G$4:$G$41,"●")/38,"0.0%")</f>
-        <v>件。新規38件の44.7%</v>
-      </c>
-      <c r="L95" s="27"/>
-      <c r="M95" s="27"/>
-    </row>
-    <row r="97" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B97" s="3" t="s">
+      <c r="E93" s="32"/>
+      <c r="F93" s="32"/>
+      <c r="G93" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B98" s="4" t="s">
+      <c r="H93" s="32"/>
+      <c r="I93" s="32"/>
+      <c r="J93" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-    </row>
-    <row r="99" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B99" s="36" t="s">
+      <c r="K93" s="32"/>
+      <c r="L93" s="32"/>
+      <c r="M93" s="32"/>
+    </row>
+    <row r="94" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B94" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C99" s="36"/>
-      <c r="D99" s="36" t="s">
+      <c r="C94" s="33"/>
+      <c r="D94" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="E99" s="36"/>
-      <c r="F99" s="36"/>
-      <c r="G99" s="36" t="s">
+      <c r="E94" s="34"/>
+      <c r="F94" s="34"/>
+      <c r="G94" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="H99" s="36"/>
-      <c r="I99" s="36"/>
-      <c r="J99" s="36" t="s">
+      <c r="H94" s="35"/>
+      <c r="I94" s="35"/>
+      <c r="J94" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="K99" s="36"/>
-      <c r="L99" s="36"/>
-      <c r="M99" s="36"/>
-    </row>
-    <row r="100" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B100" s="37" t="s">
+      <c r="K94" s="34"/>
+      <c r="L94" s="34"/>
+      <c r="M94" s="34"/>
+    </row>
+    <row r="95" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B95" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="C100" s="37"/>
-      <c r="D100" s="38" t="s">
+      <c r="C95" s="36"/>
+      <c r="D95" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E100" s="38"/>
-      <c r="F100" s="38"/>
-      <c r="G100" s="39" t="s">
+      <c r="E95" s="37"/>
+      <c r="F95" s="37"/>
+      <c r="G95" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H100" s="39"/>
-      <c r="I100" s="39"/>
-      <c r="J100" s="38" t="s">
+      <c r="H95" s="37"/>
+      <c r="I95" s="37"/>
+      <c r="J95" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="K100" s="38"/>
-      <c r="L100" s="38"/>
-      <c r="M100" s="38"/>
-    </row>
-    <row r="101" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B101" s="40" t="s">
+      <c r="K95" s="37"/>
+      <c r="L95" s="37"/>
+      <c r="M95" s="37"/>
+    </row>
+    <row r="96" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B96" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C101" s="40"/>
-      <c r="D101" s="41" t="s">
+      <c r="C96" s="36"/>
+      <c r="D96" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="E101" s="41"/>
-      <c r="F101" s="41"/>
-      <c r="G101" s="41" t="s">
+      <c r="E96" s="37"/>
+      <c r="F96" s="37"/>
+      <c r="G96" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="H101" s="41"/>
-      <c r="I101" s="41"/>
-      <c r="J101" s="41" t="s">
+      <c r="H96" s="37"/>
+      <c r="I96" s="37"/>
+      <c r="J96" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="K101" s="41"/>
-      <c r="L101" s="41"/>
-      <c r="M101" s="41"/>
-    </row>
-    <row r="102" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K96" s="37"/>
+      <c r="L96" s="37"/>
+      <c r="M96" s="37"/>
+    </row>
+    <row r="97" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B97" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C97" s="38"/>
+      <c r="D97" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E97" s="39"/>
+      <c r="F97" s="39"/>
+      <c r="G97" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="H97" s="37"/>
+      <c r="I97" s="37"/>
+      <c r="J97" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K97" s="37"/>
+      <c r="L97" s="37"/>
+      <c r="M97" s="37"/>
+    </row>
+    <row r="98" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B98" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="C98" s="38"/>
+      <c r="D98" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E98" s="37"/>
+      <c r="F98" s="37"/>
+      <c r="G98" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H98" s="37"/>
+      <c r="I98" s="37"/>
+      <c r="J98" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="K98" s="39"/>
+      <c r="L98" s="39"/>
+      <c r="M98" s="39"/>
+    </row>
+    <row r="99" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B99" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C99" s="38"/>
+      <c r="D99" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E99" s="37"/>
+      <c r="F99" s="37"/>
+      <c r="G99" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="H99" s="37"/>
+      <c r="I99" s="37"/>
+      <c r="J99" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="K99" s="39"/>
+      <c r="L99" s="39"/>
+      <c r="M99" s="39"/>
+    </row>
+    <row r="101" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B101" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C101" s="31"/>
+      <c r="D101" s="31"/>
+      <c r="E101" s="31"/>
+      <c r="F101" s="31"/>
+      <c r="G101" s="31"/>
+      <c r="H101" s="31"/>
+      <c r="I101" s="31"/>
+      <c r="J101" s="31"/>
+      <c r="K101" s="31"/>
+      <c r="L101" s="31"/>
+      <c r="M101" s="31"/>
+    </row>
+    <row r="102" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="40" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C102" s="40"/>
-      <c r="D102" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="E102" s="41"/>
-      <c r="F102" s="41"/>
-      <c r="G102" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="H102" s="41"/>
-      <c r="I102" s="41"/>
-      <c r="J102" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="K102" s="41"/>
-      <c r="L102" s="41"/>
-      <c r="M102" s="41"/>
-    </row>
-    <row r="103" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B103" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="C103" s="42"/>
-      <c r="D103" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="E103" s="43"/>
-      <c r="F103" s="43"/>
-      <c r="G103" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="H103" s="41"/>
-      <c r="I103" s="41"/>
-      <c r="J103" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="K103" s="41"/>
-      <c r="L103" s="41"/>
-      <c r="M103" s="41"/>
-    </row>
-    <row r="104" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B104" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="C104" s="42"/>
-      <c r="D104" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="E104" s="41"/>
-      <c r="F104" s="41"/>
-      <c r="G104" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="H104" s="41"/>
-      <c r="I104" s="41"/>
-      <c r="J104" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="K104" s="43"/>
-      <c r="L104" s="43"/>
-      <c r="M104" s="43"/>
-    </row>
-    <row r="105" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B105" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C105" s="42"/>
-      <c r="D105" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="E105" s="41"/>
-      <c r="F105" s="41"/>
-      <c r="G105" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="H105" s="41"/>
-      <c r="I105" s="41"/>
-      <c r="J105" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="K105" s="43"/>
-      <c r="L105" s="43"/>
-      <c r="M105" s="43"/>
-    </row>
-    <row r="107" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B107" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C107" s="31"/>
-      <c r="D107" s="31"/>
-      <c r="E107" s="31"/>
-      <c r="F107" s="31"/>
-      <c r="G107" s="31"/>
-      <c r="H107" s="31"/>
-      <c r="I107" s="31"/>
-      <c r="J107" s="31"/>
-      <c r="K107" s="31"/>
-      <c r="L107" s="31"/>
-      <c r="M107" s="31"/>
-    </row>
-    <row r="108" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B108" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C108" s="44"/>
-      <c r="D108" s="44"/>
-      <c r="E108" s="44"/>
-      <c r="F108" s="44"/>
-      <c r="G108" s="44"/>
-      <c r="H108" s="44"/>
-      <c r="I108" s="44"/>
-      <c r="J108" s="44"/>
-      <c r="K108" s="44"/>
-      <c r="L108" s="44"/>
-      <c r="M108" s="44"/>
-    </row>
-    <row r="110" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B110" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B111" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="4"/>
-      <c r="L111" s="4"/>
-      <c r="M111" s="4"/>
-    </row>
-    <row r="112" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B112" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F112" s="14"/>
-      <c r="G112" s="14"/>
-      <c r="H112" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I112" s="13"/>
-      <c r="J112" s="13"/>
-      <c r="K112" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L112" s="14"/>
-      <c r="M112" s="14"/>
-    </row>
-    <row r="113" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B113" s="8" t="n">
-        <f aca="false">SUMIF('AB玉 増減明細'!$A$4:$A$26,"建築",'AB玉 増減明細'!$E$4:$E$26)</f>
-        <v>462</v>
-      </c>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="29" t="n">
-        <f aca="false">SUMIF('CD玉 増減明細'!$A$4:$A$23,"建築",'CD玉 増減明細'!$E$4:$E$23)</f>
-        <v>0</v>
-      </c>
-      <c r="F113" s="29"/>
-      <c r="G113" s="29"/>
-      <c r="H113" s="45" t="n">
-        <f aca="false">SUMIF(成約明細!$A$4:$A$22,"建築",成約明細!$C$4:$C$22)</f>
-        <v>535</v>
-      </c>
-      <c r="I113" s="45"/>
-      <c r="J113" s="45"/>
-      <c r="K113" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="L113" s="46"/>
-      <c r="M113" s="46"/>
-    </row>
-    <row r="114" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B114" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C114" s="19"/>
-      <c r="D114" s="19"/>
-      <c r="E114" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="F114" s="20"/>
-      <c r="G114" s="20"/>
-      <c r="H114" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="I114" s="11"/>
-      <c r="J114" s="11"/>
-      <c r="K114" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="L114" s="20"/>
-      <c r="M114" s="20"/>
-    </row>
-    <row r="116" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B116" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="3"/>
-      <c r="L116" s="3"/>
-      <c r="M116" s="3"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B117" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
-      <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
-      <c r="J117" s="4"/>
-      <c r="K117" s="4"/>
-      <c r="L117" s="4"/>
-      <c r="M117" s="4"/>
-    </row>
-    <row r="118" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B118" s="47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C118" s="47"/>
-      <c r="D118" s="47"/>
-      <c r="E118" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="F118" s="47"/>
-      <c r="G118" s="47"/>
-      <c r="H118" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="I118" s="47"/>
-      <c r="J118" s="47"/>
-      <c r="K118" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="L118" s="47"/>
-      <c r="M118" s="47"/>
-    </row>
-    <row r="119" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B119" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C119" s="48"/>
-      <c r="D119" s="48"/>
-      <c r="E119" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="F119" s="48"/>
-      <c r="G119" s="48"/>
-      <c r="H119" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="I119" s="49"/>
-      <c r="J119" s="49"/>
-      <c r="K119" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="L119" s="48"/>
-      <c r="M119" s="48"/>
-    </row>
-    <row r="120" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B120" s="48"/>
-      <c r="C120" s="48"/>
-      <c r="D120" s="48"/>
-      <c r="E120" s="48"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="48"/>
-      <c r="H120" s="49"/>
-      <c r="I120" s="49"/>
-      <c r="J120" s="49"/>
-      <c r="K120" s="48"/>
-      <c r="L120" s="48"/>
-      <c r="M120" s="48"/>
+      <c r="D102" s="40"/>
+      <c r="E102" s="40"/>
+      <c r="F102" s="40"/>
+      <c r="G102" s="40"/>
+      <c r="H102" s="40"/>
+      <c r="I102" s="40"/>
+      <c r="J102" s="40"/>
+      <c r="K102" s="40"/>
+      <c r="L102" s="40"/>
+      <c r="M102" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="126">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="B5:M5"/>
@@ -12869,74 +12093,36 @@
     <mergeCell ref="B89:M89"/>
     <mergeCell ref="B91:M91"/>
     <mergeCell ref="B92:M92"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="H93:J93"/>
-    <mergeCell ref="K93:M93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="E94:G94"/>
-    <mergeCell ref="H94:J94"/>
-    <mergeCell ref="K94:M94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="E95:G95"/>
-    <mergeCell ref="H95:J95"/>
-    <mergeCell ref="K95:M95"/>
-    <mergeCell ref="B97:M97"/>
-    <mergeCell ref="B98:M98"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="J93:M93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="J94:M94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="J95:M95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="J96:M96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="G97:I97"/>
+    <mergeCell ref="J97:M97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="G98:I98"/>
+    <mergeCell ref="J98:M98"/>
     <mergeCell ref="B99:C99"/>
     <mergeCell ref="D99:F99"/>
     <mergeCell ref="G99:I99"/>
     <mergeCell ref="J99:M99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="J100:M100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="G101:I101"/>
-    <mergeCell ref="J101:M101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="G102:I102"/>
-    <mergeCell ref="J102:M102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="G103:I103"/>
-    <mergeCell ref="J103:M103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="G104:I104"/>
-    <mergeCell ref="J104:M104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="G105:I105"/>
-    <mergeCell ref="J105:M105"/>
-    <mergeCell ref="B107:M107"/>
-    <mergeCell ref="B108:M108"/>
-    <mergeCell ref="B110:M110"/>
-    <mergeCell ref="B111:M111"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="E112:G112"/>
-    <mergeCell ref="H112:J112"/>
-    <mergeCell ref="K112:M112"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="H113:J113"/>
-    <mergeCell ref="K113:M113"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="E114:G114"/>
-    <mergeCell ref="H114:J114"/>
-    <mergeCell ref="K114:M114"/>
-    <mergeCell ref="B116:M116"/>
-    <mergeCell ref="B117:M117"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="E118:G118"/>
-    <mergeCell ref="H118:J118"/>
-    <mergeCell ref="K118:M118"/>
-    <mergeCell ref="B119:D120"/>
-    <mergeCell ref="E119:G120"/>
-    <mergeCell ref="H119:J120"/>
-    <mergeCell ref="K119:M120"/>
+    <mergeCell ref="B101:M101"/>
+    <mergeCell ref="B102:M102"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12984,637 +12170,637 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="42" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="46" t="n">
+        <v>7616</v>
+      </c>
+      <c r="E4" s="47" t="n">
+        <v>7616</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="50" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E5" s="51" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>1128</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="50" t="n">
+        <v>545</v>
+      </c>
+      <c r="E7" s="51" t="n">
+        <v>545</v>
+      </c>
+      <c r="F7" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>462</v>
+      </c>
+      <c r="E8" s="47" t="n">
+        <v>462</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="50" t="n">
+        <v>430</v>
+      </c>
+      <c r="E9" s="51" t="n">
+        <v>430</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>265</v>
+      </c>
+      <c r="E10" s="47" t="n">
+        <v>265</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="49" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="51" t="s">
+      <c r="C11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="50" t="n">
+        <v>220</v>
+      </c>
+      <c r="E11" s="51" t="n">
+        <v>220</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="52" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="52" t="s">
+      <c r="H11" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="C12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>173</v>
+      </c>
+      <c r="E12" s="47" t="n">
+        <v>173</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="E13" s="51" t="n">
+        <v>150</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="C14" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>149</v>
+      </c>
+      <c r="E14" s="47" t="n">
+        <v>149</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="52" t="s">
+      <c r="C15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="E15" s="51" t="n">
+        <v>120</v>
+      </c>
+      <c r="F15" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="C16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="46" t="n">
+        <v>98</v>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="C17" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="50" t="n">
+        <v>70</v>
+      </c>
+      <c r="E17" s="51" t="n">
+        <v>70</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="45" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="54" t="s">
+      <c r="C18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="46" t="n">
+        <v>62</v>
+      </c>
+      <c r="E18" s="47" t="n">
+        <v>62</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="C19" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="50" t="n">
+        <v>62</v>
+      </c>
+      <c r="E19" s="51" t="n">
+        <v>62</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="55" t="n">
+      <c r="C20" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="55" t="n">
-        <v>7616</v>
-      </c>
-      <c r="E4" s="56" t="n">
-        <v>7616</v>
-      </c>
-      <c r="F4" s="54" t="s">
+      <c r="D20" s="46" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="C21" s="50" t="n">
+        <v>1570</v>
+      </c>
+      <c r="D21" s="50" t="n">
+        <v>1616</v>
+      </c>
+      <c r="E21" s="51" t="n">
+        <v>46</v>
+      </c>
+      <c r="F21" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="C22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>38</v>
+      </c>
+      <c r="E22" s="47" t="n">
+        <v>38</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="52" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="58" t="s">
+      <c r="C23" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="50" t="n">
+        <v>37</v>
+      </c>
+      <c r="E23" s="51" t="n">
+        <v>37</v>
+      </c>
+      <c r="F23" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="59" t="n">
+      <c r="C24" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="59" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E5" s="60" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F5" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G5" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H5" s="61" t="s">
+      <c r="D24" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="49" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="57" t="s">
+      <c r="C25" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="55" t="n">
-        <v>1128</v>
-      </c>
-      <c r="E6" s="56" t="n">
-        <v>1128</v>
-      </c>
-      <c r="F6" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="57" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="59" t="n">
-        <v>545</v>
-      </c>
-      <c r="E7" s="60" t="n">
-        <v>545</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H7" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="55" t="n">
-        <v>462</v>
-      </c>
-      <c r="E8" s="56" t="n">
-        <v>462</v>
-      </c>
-      <c r="F8" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="59" t="n">
-        <v>430</v>
-      </c>
-      <c r="E9" s="60" t="n">
-        <v>430</v>
-      </c>
-      <c r="F9" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G9" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="55" t="n">
-        <v>265</v>
-      </c>
-      <c r="E10" s="56" t="n">
-        <v>265</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="59" t="n">
-        <v>220</v>
-      </c>
-      <c r="E11" s="60" t="n">
-        <v>220</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="61" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="55" t="n">
-        <v>173</v>
-      </c>
-      <c r="E12" s="56" t="n">
-        <v>173</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="59" t="n">
-        <v>150</v>
-      </c>
-      <c r="E13" s="60" t="n">
-        <v>150</v>
-      </c>
-      <c r="F13" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H13" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="55" t="n">
-        <v>149</v>
-      </c>
-      <c r="E14" s="56" t="n">
-        <v>149</v>
-      </c>
-      <c r="F14" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H14" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="E15" s="60" t="n">
-        <v>120</v>
-      </c>
-      <c r="F15" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="55" t="n">
-        <v>98</v>
-      </c>
-      <c r="E16" s="56" t="n">
-        <v>98</v>
-      </c>
-      <c r="F16" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="59" t="n">
-        <v>70</v>
-      </c>
-      <c r="E17" s="60" t="n">
-        <v>70</v>
-      </c>
-      <c r="F17" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="55" t="n">
-        <v>62</v>
-      </c>
-      <c r="E18" s="56" t="n">
-        <v>62</v>
-      </c>
-      <c r="F18" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="59" t="n">
-        <v>62</v>
-      </c>
-      <c r="E19" s="60" t="n">
-        <v>62</v>
-      </c>
-      <c r="F19" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="C20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="55" t="n">
-        <v>50</v>
-      </c>
-      <c r="E20" s="56" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="C21" s="59" t="n">
-        <v>1570</v>
-      </c>
-      <c r="D21" s="59" t="n">
-        <v>1616</v>
-      </c>
-      <c r="E21" s="60" t="n">
-        <v>46</v>
-      </c>
-      <c r="F21" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="H21" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="55" t="n">
-        <v>38</v>
-      </c>
-      <c r="E22" s="56" t="n">
-        <v>38</v>
-      </c>
-      <c r="F22" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="59" t="n">
-        <v>37</v>
-      </c>
-      <c r="E23" s="60" t="n">
-        <v>37</v>
-      </c>
-      <c r="F23" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="H23" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B24" s="54" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="55" t="n">
-        <v>12</v>
-      </c>
-      <c r="E24" s="56" t="n">
-        <v>12</v>
-      </c>
-      <c r="F24" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="58" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="H25" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="55" t="n">
+      <c r="C26" s="46" t="n">
         <v>2000</v>
       </c>
-      <c r="D26" s="55" t="n">
+      <c r="D26" s="46" t="n">
         <v>1950</v>
       </c>
-      <c r="E26" s="56" t="n">
+      <c r="E26" s="47" t="n">
         <v>-50</v>
       </c>
-      <c r="F26" s="54" t="s">
+      <c r="F26" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="H26" s="57" t="s">
-        <v>109</v>
+      <c r="G26" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="48" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -13645,559 +12831,559 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
-        <v>134</v>
+      <c r="A1" s="41" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="51" t="s">
-        <v>135</v>
+      <c r="A2" s="42" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>136</v>
-      </c>
-      <c r="D3" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="52" t="s">
+      <c r="A3" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="F3" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="46" t="n">
+        <v>5834</v>
+      </c>
+      <c r="E4" s="47" t="n">
+        <v>5834</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="50" t="n">
+        <v>1649</v>
+      </c>
+      <c r="E5" s="51" t="n">
+        <v>1649</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="50" t="n">
+        <v>390</v>
+      </c>
+      <c r="E7" s="51" t="n">
+        <v>390</v>
+      </c>
+      <c r="F7" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>360</v>
+      </c>
+      <c r="E8" s="47" t="n">
+        <v>360</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="50" t="n">
+        <v>920</v>
+      </c>
+      <c r="D9" s="50" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E9" s="51" t="n">
+        <v>330</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>235</v>
+      </c>
+      <c r="E10" s="47" t="n">
+        <v>235</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="E11" s="51" t="n">
+        <v>120</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="53" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="55" t="n">
+      <c r="C13" s="50" t="n">
+        <v>106</v>
+      </c>
+      <c r="D13" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="55" t="n">
-        <v>5834</v>
-      </c>
-      <c r="E4" s="56" t="n">
-        <v>5834</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H4" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="59" t="n">
+      <c r="E13" s="51" t="n">
+        <v>-106</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>140</v>
+      </c>
+      <c r="D14" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="59" t="n">
-        <v>1649</v>
-      </c>
-      <c r="E5" s="60" t="n">
-        <v>1649</v>
-      </c>
-      <c r="F5" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="H5" s="61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="55" t="n">
+      <c r="E14" s="47" t="n">
+        <v>-140</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="50" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="51" t="n">
+        <v>-300</v>
+      </c>
+      <c r="F15" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="50" t="n">
+        <v>785</v>
+      </c>
+      <c r="D17" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="51" t="n">
+        <v>-785</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>800</v>
+      </c>
+      <c r="D18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="47" t="n">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="50" t="n">
         <v>1000</v>
       </c>
-      <c r="D6" s="55" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E6" s="56" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F6" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="H6" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="59" t="n">
+      <c r="D19" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="59" t="n">
-        <v>390</v>
-      </c>
-      <c r="E7" s="60" t="n">
-        <v>390</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H7" s="61" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="55" t="n">
+      <c r="E19" s="51" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="55" t="n">
-        <v>360</v>
-      </c>
-      <c r="E8" s="56" t="n">
-        <v>360</v>
-      </c>
-      <c r="F8" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="59" t="n">
-        <v>920</v>
-      </c>
-      <c r="D9" s="59" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E9" s="60" t="n">
-        <v>330</v>
-      </c>
-      <c r="F9" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" s="61" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="55" t="n">
+      <c r="E20" s="47" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="50" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D21" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="55" t="n">
-        <v>235</v>
-      </c>
-      <c r="E10" s="56" t="n">
-        <v>235</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="59" t="n">
+      <c r="E21" s="51" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="F21" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>1572</v>
+      </c>
+      <c r="D22" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="E11" s="60" t="n">
-        <v>120</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" s="61" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="55" t="n">
+      <c r="E22" s="47" t="n">
+        <v>-1572</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="50" t="n">
+        <v>3352</v>
+      </c>
+      <c r="D23" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="55" t="n">
-        <v>80</v>
-      </c>
-      <c r="E12" s="56" t="n">
-        <v>80</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="59" t="n">
-        <v>106</v>
-      </c>
-      <c r="D13" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="60" t="n">
-        <v>-106</v>
-      </c>
-      <c r="F13" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H13" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="55" t="n">
-        <v>140</v>
-      </c>
-      <c r="D14" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="56" t="n">
-        <v>-140</v>
-      </c>
-      <c r="F14" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="59" t="n">
-        <v>300</v>
-      </c>
-      <c r="D15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="60" t="n">
-        <v>-300</v>
-      </c>
-      <c r="F15" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" s="61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="55" t="n">
-        <v>500</v>
-      </c>
-      <c r="D16" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="56" t="n">
-        <v>-500</v>
-      </c>
-      <c r="F16" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="G16" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="H16" s="57" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="58" t="s">
-        <v>148</v>
-      </c>
-      <c r="C17" s="59" t="n">
-        <v>785</v>
-      </c>
-      <c r="D17" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="60" t="n">
-        <v>-785</v>
-      </c>
-      <c r="F17" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="61" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="55" t="n">
-        <v>800</v>
-      </c>
-      <c r="D18" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="56" t="n">
-        <v>-800</v>
-      </c>
-      <c r="F18" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="H18" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D19" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="60" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="F19" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G19" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H19" s="61" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" s="55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D20" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="56" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="F20" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="H20" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" s="59" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D21" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="60" t="n">
-        <v>-1300</v>
-      </c>
-      <c r="F21" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" s="61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="C22" s="55" t="n">
-        <v>1572</v>
-      </c>
-      <c r="D22" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="56" t="n">
-        <v>-1572</v>
-      </c>
-      <c r="F22" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="H22" s="57" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="59" t="n">
-        <v>3352</v>
-      </c>
-      <c r="D23" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="60" t="n">
+      <c r="E23" s="51" t="n">
         <v>-3352</v>
       </c>
-      <c r="F23" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="H23" s="61" t="s">
-        <v>109</v>
+      <c r="F23" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -14227,353 +13413,353 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="53" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>3640</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="50" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="50" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>1475</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="50" t="n">
+        <v>1384</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>535</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="50" t="n">
+        <v>430</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>265</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="50" t="n">
+        <v>173</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>150</v>
+      </c>
+      <c r="D14" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="50" t="n">
+        <v>149</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>120</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="50" t="n">
+        <v>70</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>62</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="50" t="n">
+        <v>62</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="52" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="62" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>38</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" s="48" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="52" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="52" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="48" t="s">
         <v>156</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="55" t="n">
-        <v>3640</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="59" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="61" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="55" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="59" t="n">
-        <v>1950</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>163</v>
-      </c>
-      <c r="E7" s="61" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8" s="55" t="n">
-        <v>1475</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="57" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" s="59" t="n">
-        <v>1384</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>163</v>
-      </c>
-      <c r="E9" s="61" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="55" t="n">
-        <v>535</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" s="59" t="n">
-        <v>430</v>
-      </c>
-      <c r="D11" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="61" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="C12" s="55" t="n">
-        <v>265</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="59" t="n">
-        <v>173</v>
-      </c>
-      <c r="D13" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="61" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="55" t="n">
-        <v>150</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="59" t="n">
-        <v>149</v>
-      </c>
-      <c r="D15" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="61" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="55" t="n">
-        <v>120</v>
-      </c>
-      <c r="D16" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="59" t="n">
-        <v>70</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="61" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="55" t="n">
-        <v>62</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" s="59" t="n">
-        <v>62</v>
-      </c>
-      <c r="D19" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="61" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" s="55" t="n">
-        <v>38</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="58" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" s="61" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="54" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="57" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -14604,868 +13790,868 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="53" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="46" t="n">
+        <v>5834</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="45"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="50" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="49"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="50" t="n">
+        <v>462</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="49"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>360</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="G8" s="45"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="50" t="n">
+        <v>265</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="49"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>235</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="45"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="50" t="n">
+        <v>173</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="G11" s="49"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>149</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" s="45"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="50" t="n">
+        <v>120</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" s="49"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>120</v>
+      </c>
+      <c r="D14" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="G14" s="45"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="50" t="n">
+        <v>98</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="G15" s="49"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>80</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="45"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="50" t="n">
+        <v>62</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="F17" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="G17" s="49"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>62</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" s="45"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="G19" s="49"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="G20" s="45"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="50" t="n">
+        <v>38</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="49"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>37</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="45"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="49"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="G24" s="45"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="G26" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="45" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="62" t="s">
+      <c r="C28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="48" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="52" t="s">
+      <c r="G28" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="C29" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F29" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="G29" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="C30" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="G30" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="49" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="55" t="n">
-        <v>5834</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="57" t="s">
+      <c r="C31" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="54"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="58" t="s">
+      <c r="G31" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="59" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F5" s="61" t="s">
+      <c r="C32" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="G32" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="G5" s="58"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="55" t="n">
-        <v>1128</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="57" t="s">
+      <c r="C33" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F33" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="G6" s="54"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="58" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="59" t="n">
-        <v>462</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F7" s="61" t="s">
+      <c r="C34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="G34" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="G7" s="58"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="55" t="n">
-        <v>360</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="G8" s="54"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="59" t="n">
-        <v>265</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="61" t="s">
+      <c r="C35" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="G35" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="C36" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="G9" s="58"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="55" t="n">
-        <v>235</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" s="57" t="s">
+      <c r="G36" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="G10" s="54"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="59" t="n">
-        <v>173</v>
-      </c>
-      <c r="D11" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="G11" s="58"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="55" t="n">
-        <v>149</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="G12" s="54"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="59" t="n">
-        <v>120</v>
-      </c>
-      <c r="D13" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="G13" s="58"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="55" t="n">
-        <v>120</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="F14" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="G14" s="54"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="59" t="n">
-        <v>98</v>
-      </c>
-      <c r="D15" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="F15" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="G15" s="58"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="C16" s="55" t="n">
+      <c r="C37" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="G37" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="G16" s="54"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="59" t="n">
-        <v>62</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="F17" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="G17" s="58"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="C18" s="55" t="n">
-        <v>62</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="G18" s="54"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="C19" s="59" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="61" t="s">
+      <c r="B38" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F38" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="F19" s="61" t="s">
-        <v>195</v>
-      </c>
-      <c r="G19" s="58"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="C20" s="55" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="G20" s="54"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="C21" s="59" t="n">
-        <v>38</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="F21" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="G21" s="58"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="55" t="n">
-        <v>37</v>
-      </c>
-      <c r="D22" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="F22" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="G22" s="54"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="58" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="F23" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="G23" s="58"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B24" s="54" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="D24" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" s="57" t="s">
-        <v>191</v>
-      </c>
-      <c r="F24" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="G24" s="54"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="58" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="59" t="n">
+      <c r="G39" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="C40" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="G25" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="54" t="s">
+      <c r="D40" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="G40" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="55" t="n">
+      <c r="C41" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F26" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="G26" s="57" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="C27" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="G27" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" s="54" t="s">
-        <v>203</v>
-      </c>
-      <c r="C28" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F28" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="G28" s="57" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="58" t="s">
-        <v>205</v>
-      </c>
-      <c r="C29" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="G29" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="54" t="s">
-        <v>207</v>
-      </c>
-      <c r="C30" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F30" s="57" t="s">
-        <v>206</v>
-      </c>
-      <c r="G30" s="57" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="58" t="s">
-        <v>208</v>
-      </c>
-      <c r="C31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F31" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="G31" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B32" s="54" t="s">
-        <v>210</v>
-      </c>
-      <c r="C32" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F32" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="G32" s="57" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" s="58" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F33" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="G33" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="54" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F34" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="G34" s="57" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="58" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F35" s="61" t="s">
-        <v>189</v>
-      </c>
-      <c r="G35" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="C36" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E36" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F36" s="57" t="s">
-        <v>215</v>
-      </c>
-      <c r="G36" s="57" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B37" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="C37" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F37" s="61" t="s">
-        <v>217</v>
-      </c>
-      <c r="G37" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B38" s="54" t="s">
-        <v>218</v>
-      </c>
-      <c r="C38" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F38" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="G38" s="57" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B39" s="58" t="s">
-        <v>219</v>
-      </c>
-      <c r="C39" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E39" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="F39" s="61" t="s">
-        <v>186</v>
-      </c>
-      <c r="G39" s="61" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B40" s="54" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F40" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="G40" s="57" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" s="58" t="s">
-        <v>222</v>
-      </c>
-      <c r="C41" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F41" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="G41" s="61" t="s">
-        <v>198</v>
+      <c r="D41" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="F41" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="G41" s="52" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -15495,183 +14681,183 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
-        <v>223</v>
+      <c r="A1" s="41" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="62" t="s">
-        <v>224</v>
+      <c r="A2" s="53" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>225</v>
+      <c r="A3" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="55" t="n">
+      <c r="A4" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="46" t="n">
         <v>1572</v>
       </c>
-      <c r="D4" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>159</v>
+      <c r="D4" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="59" t="n">
+      <c r="A5" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="50" t="n">
         <v>1300</v>
       </c>
-      <c r="D5" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="61" t="s">
-        <v>159</v>
+      <c r="D5" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="55" t="n">
+      <c r="A6" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="46" t="n">
         <v>1000</v>
       </c>
-      <c r="D6" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>220</v>
+      <c r="D6" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="58" t="s">
+      <c r="A7" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="50" t="n">
+        <v>800</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>785</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="50" t="n">
+        <v>140</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="59" t="n">
-        <v>800</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="61" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="55" t="n">
-        <v>785</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="57" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="61" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="59" t="n">
-        <v>140</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="61" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="55" t="n">
+      <c r="A10" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>159</v>
+      <c r="D10" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>227</v>
-      </c>
-      <c r="C11" s="59" t="n">
+      <c r="A11" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="61" t="s">
-        <v>220</v>
+      <c r="D11" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="C12" s="55" t="n">
+      <c r="A12" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>159</v>
+      <c r="D12" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -15698,183 +14884,183 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
-        <v>229</v>
+      <c r="A1" s="54" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="62" t="s">
-        <v>230</v>
+      <c r="A2" s="53" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="65" t="s">
-        <v>233</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>234</v>
-      </c>
-      <c r="E4" s="65" t="s">
-        <v>235</v>
+      <c r="A4" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" s="56" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="B5" s="67" t="n">
+      <c r="A5" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="58" t="n">
         <f aca="false">B6-SUMIF('AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON",'AB玉 増減明細'!$E$4:$E$26)</f>
         <v>85087</v>
       </c>
-      <c r="C5" s="67" t="n">
+      <c r="C5" s="58" t="n">
         <f aca="false">C6-SUMIF('CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON",'CD玉 増減明細'!$E$4:$E$23)</f>
         <v>184157</v>
       </c>
-      <c r="D5" s="68" t="n">
+      <c r="D5" s="59" t="n">
         <v>300</v>
       </c>
-      <c r="E5" s="69" t="n">
+      <c r="E5" s="60" t="n">
         <f aca="false">SUM(B5:D5)</f>
         <v>269544</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="B6" s="68" t="n">
+      <c r="A6" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="59" t="n">
         <v>99318</v>
       </c>
-      <c r="C6" s="68" t="n">
+      <c r="C6" s="59" t="n">
         <v>183800</v>
       </c>
-      <c r="D6" s="68" t="n">
+      <c r="D6" s="59" t="n">
         <v>300</v>
       </c>
-      <c r="E6" s="69" t="n">
+      <c r="E6" s="60" t="n">
         <f aca="false">SUM(B6:D6)</f>
         <v>283418</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="71" t="n">
+      <c r="B7" s="62" t="n">
         <f aca="false">B6-B5</f>
         <v>14231</v>
       </c>
-      <c r="C7" s="71" t="n">
+      <c r="C7" s="62" t="n">
         <f aca="false">C6-C5</f>
         <v>-357</v>
       </c>
-      <c r="D7" s="71" t="n">
+      <c r="D7" s="62" t="n">
         <f aca="false">D6-D5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="71" t="n">
+      <c r="E7" s="62" t="n">
         <f aca="false">E6-E5</f>
         <v>13874</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="72" t="s">
-        <v>238</v>
+      <c r="A9" s="63" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="67" t="n">
+      <c r="A10" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="58" t="n">
         <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"確度UP（CD→AB）",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>11811</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="67" t="n">
+      <c r="B11" s="58" t="n">
         <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"新規作成",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>2204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="B12" s="67" t="n">
+      <c r="A12" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="58" t="n">
         <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"失注から復活",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")+SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"増額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="73" t="s">
-        <v>240</v>
-      </c>
-      <c r="B13" s="74" t="n">
+      <c r="A13" s="64" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="65" t="n">
         <f aca="false">SUMIFS('AB玉 増減明細'!$E$4:$E$26,'AB玉 増減明細'!$F$4:$F$26,"減額",'AB玉 増減明細'!$A$4:$A$26,"コーデ+TREEBATON")</f>
         <v>-50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="72" t="s">
-        <v>241</v>
+      <c r="A16" s="63" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="67" t="n">
+      <c r="B17" s="58" t="n">
         <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"新規作成",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
         <v>6629</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="67" t="n">
+      <c r="B18" s="58" t="n">
         <f aca="false">SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"増額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON")</f>
         <v>3869</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="75" t="s">
-        <v>242</v>
+      <c r="A20" s="66" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="67" t="n">
+      <c r="B21" s="58" t="n">
         <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"失注",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
         <v>5597</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="54" t="s">
-        <v>243</v>
-      </c>
-      <c r="B22" s="67" t="n">
+      <c r="A22" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="B22" s="58" t="n">
         <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"確度UP（CD→AB）",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
         <v>5258</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="67" t="n">
+      <c r="B23" s="58" t="n">
         <f aca="false">ABS(SUMIFS('CD玉 増減明細'!$E$4:$E$23,'CD玉 増減明細'!$F$4:$F$23,"減額",'CD玉 増減明細'!$A$4:$A$23,"コーデ+TREEBATON"))</f>
         <v>0</v>
       </c>
@@ -15903,206 +15089,206 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="54" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="67" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="68"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="69" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="70" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="69" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="70" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="71"/>
+      <c r="B7" s="70"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="70"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="70" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="72" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" s="70" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="69" t="s">
+        <v>211</v>
+      </c>
+      <c r="B12" s="70" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="69" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" s="68" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="71"/>
+      <c r="B14" s="70"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" s="70"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="72" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="68" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="72" t="s">
+        <v>242</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="72" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="76" t="s">
+      <c r="B18" s="68" t="s">
         <v>245</v>
       </c>
-      <c r="B3" s="77"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="78" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="72" t="s">
         <v>246</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B19" s="70" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="78" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="69" t="s">
         <v>248</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B20" s="68" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="78" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="71"/>
+      <c r="B21" s="70"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="67" t="s">
         <v>250</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B22" s="70"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="69" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="80"/>
-      <c r="B7" s="79"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="76" t="s">
+      <c r="B23" s="70" t="s">
         <v>252</v>
       </c>
-      <c r="B8" s="79"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="81" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="69" t="s">
         <v>253</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B24" s="70" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="81" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="71"/>
+      <c r="B25" s="70"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="67" t="s">
         <v>255</v>
       </c>
-      <c r="B10" s="79" t="s">
+      <c r="B26" s="70"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="69" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="81" t="s">
+      <c r="B27" s="70" t="s">
         <v>257</v>
       </c>
-      <c r="B11" s="79" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="69" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="70" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="78" t="s">
-        <v>234</v>
-      </c>
-      <c r="B12" s="79" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="69" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="78" t="s">
+      <c r="B29" s="70" t="s">
         <v>260</v>
       </c>
-      <c r="B13" s="77" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="72" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="80"/>
-      <c r="B14" s="79"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="76" t="s">
+      <c r="B30" s="68" t="s">
         <v>262</v>
-      </c>
-      <c r="B15" s="79"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="81" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="77" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="81" t="s">
-        <v>265</v>
-      </c>
-      <c r="B17" s="77" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="81" t="s">
-        <v>267</v>
-      </c>
-      <c r="B18" s="77" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="81" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="79" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="78" t="s">
-        <v>271</v>
-      </c>
-      <c r="B20" s="77" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="80"/>
-      <c r="B21" s="79"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="76" t="s">
-        <v>273</v>
-      </c>
-      <c r="B22" s="79"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="78" t="s">
-        <v>274</v>
-      </c>
-      <c r="B23" s="79" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="78" t="s">
-        <v>276</v>
-      </c>
-      <c r="B24" s="79" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="80"/>
-      <c r="B25" s="79"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="76" t="s">
-        <v>278</v>
-      </c>
-      <c r="B26" s="79"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="78" t="s">
-        <v>279</v>
-      </c>
-      <c r="B27" s="79" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="78" t="s">
-        <v>185</v>
-      </c>
-      <c r="B28" s="79" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="78" t="s">
-        <v>282</v>
-      </c>
-      <c r="B29" s="79" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="81" t="s">
-        <v>284</v>
-      </c>
-      <c r="B30" s="77" t="s">
-        <v>285</v>
       </c>
     </row>
   </sheetData>
